--- a/public/images/items/ingredienten_categorieen.xlsx
+++ b/public/images/items/ingredienten_categorieen.xlsx
@@ -2512,1851 +2512,3491 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B230"/>
+  <dimension ref="A1:I120"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Synoniem</v>
+        <v>Afbeelding (png / slug)</v>
       </c>
       <c r="B1" t="str">
-        <v>Slug</v>
+        <v>Synoniem 1</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Synoniem 2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Synoniem 3</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Synoniem 4</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Synoniem 5</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Synoniem 6</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Synoniem 7</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Synoniem 8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>aardappelen</v>
+      </c>
+      <c r="B2" t="str">
         <v>aardappel</v>
       </c>
-      <c r="B2" t="str">
-        <v>aardappelen</v>
+      <c r="C2" t="str">
+        <v>aardappels</v>
+      </c>
+      <c r="D2" t="str">
+        <v>aardappeltje</v>
+      </c>
+      <c r="E2" t="str">
+        <v>aardappeltjes</v>
+      </c>
+      <c r="F2" t="str">
+        <v>frietaardappelen</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>aardappels</v>
+        <v>aardbeien</v>
       </c>
       <c r="B3" t="str">
-        <v>aardappelen</v>
+        <v>aardbei</v>
+      </c>
+      <c r="C3" t="str">
+        <v>aardbeien</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>aardappeltje</v>
+        <v>ajuinen</v>
       </c>
       <c r="B4" t="str">
-        <v>aardappelen</v>
+        <v>ajuin</v>
+      </c>
+      <c r="C4" t="str">
+        <v>gesnipperde ui</v>
+      </c>
+      <c r="D4" t="str">
+        <v>ui</v>
+      </c>
+      <c r="E4" t="str">
+        <v>ui gesnipperd</v>
+      </c>
+      <c r="F4" t="str">
+        <v>uien</v>
+      </c>
+      <c r="G4" t="str">
+        <v>uienringen</v>
+      </c>
+      <c r="H4" t="str">
+        <v>uitje</v>
+      </c>
+      <c r="I4" t="str">
+        <v>uitjes</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>aardappeltjes</v>
+        <v>amandelen</v>
       </c>
       <c r="B5" t="str">
-        <v>aardappelen</v>
+        <v>amandel</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>frietaardappelen</v>
+        <v>appels_1</v>
       </c>
       <c r="B6" t="str">
-        <v>aardappelen</v>
+        <v>appel</v>
+      </c>
+      <c r="C6" t="str">
+        <v>appels</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>aardbei</v>
+        <v>arachideolie</v>
       </c>
       <c r="B7" t="str">
-        <v>aardbeien</v>
+        <v>arachide olie</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>aardbeien</v>
+        <v>augurken</v>
       </c>
       <c r="B8" t="str">
-        <v>aardbeien</v>
+        <v>augurk</v>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ajuin</v>
+        <v>avocado</v>
       </c>
       <c r="B9" t="str">
-        <v>ajuinen</v>
+        <v>avocado</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>gesnipperde ui</v>
+        <v>bananen</v>
       </c>
       <c r="B10" t="str">
-        <v>ajuinen</v>
+        <v>banaan</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ui</v>
+        <v>basilicum</v>
       </c>
       <c r="B11" t="str">
-        <v>ajuinen</v>
+        <v>verse basilicum</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ui gesnipperd</v>
+        <v>bieslook</v>
       </c>
       <c r="B12" t="str">
-        <v>ajuinen</v>
+        <v>verse bieslook</v>
+      </c>
+      <c r="C12" t="str">
+        <v/>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>uien</v>
+        <v>blik_tomaten</v>
       </c>
       <c r="B13" t="str">
-        <v>ajuinen</v>
+        <v>gepelde tomaten</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ingeblikte tomaten</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>uienringen</v>
+        <v>bloemsuiker</v>
       </c>
       <c r="B14" t="str">
-        <v>ajuinen</v>
+        <v>poedersuiker</v>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>uitje</v>
+        <v>bosbessen</v>
       </c>
       <c r="B15" t="str">
-        <v>ajuinen</v>
+        <v>blauwe bes</v>
+      </c>
+      <c r="C15" t="str">
+        <v>blauwe bessen</v>
+      </c>
+      <c r="D15" t="str">
+        <v>bosbes</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>uitjes</v>
+        <v>bouillon</v>
       </c>
       <c r="B16" t="str">
-        <v>ajuinen</v>
+        <v>bouillon blokje</v>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>amandel</v>
+        <v>bruine_suiker</v>
       </c>
       <c r="B17" t="str">
-        <v>amandelen</v>
+        <v>basterdsuiker</v>
+      </c>
+      <c r="C17" t="str">
+        <v>bruine suiker</v>
+      </c>
+      <c r="D17" t="str">
+        <v>cassonade</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>appel</v>
+        <v>butternut</v>
       </c>
       <c r="B18" t="str">
-        <v>appels_1</v>
+        <v>butternut squash</v>
+      </c>
+      <c r="C18" t="str">
+        <v>pompoen</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>appels</v>
+        <v>cacao</v>
       </c>
       <c r="B19" t="str">
-        <v>appels_1</v>
+        <v>cacao poeder</v>
+      </c>
+      <c r="C19" t="str">
+        <v>cacaopoeder</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>arachide olie</v>
+        <v>cappelini</v>
       </c>
       <c r="B20" t="str">
-        <v>arachideolie</v>
+        <v>spaghetti</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>augurk</v>
+        <v>champignons</v>
       </c>
       <c r="B21" t="str">
-        <v>augurken</v>
+        <v>champignon</v>
+      </c>
+      <c r="C21" t="str">
+        <v>paddenstoel</v>
+      </c>
+      <c r="D21" t="str">
+        <v>paddenstoelen</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>avocado</v>
+        <v>chilipepers</v>
       </c>
       <c r="B22" t="str">
-        <v>avocado</v>
+        <v>chili</v>
+      </c>
+      <c r="C22" t="str">
+        <v>chilivlokken</v>
+      </c>
+      <c r="D22" t="str">
+        <v>rode peper</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>banaan</v>
+        <v>chocolade</v>
       </c>
       <c r="B23" t="str">
-        <v>bananen</v>
+        <v>melkchocolade</v>
+      </c>
+      <c r="C23" t="str">
+        <v>pure chocolade</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>verse basilicum</v>
+        <v>citroen</v>
       </c>
       <c r="B24" t="str">
-        <v>basilicum</v>
+        <v>citroensap</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>verse bieslook</v>
+        <v>curry</v>
       </c>
       <c r="B25" t="str">
-        <v>bieslook</v>
+        <v>currypoeder</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>gepelde tomaten</v>
+        <v>eieren_1</v>
       </c>
       <c r="B26" t="str">
-        <v>blik_tomaten</v>
+        <v>ei</v>
+      </c>
+      <c r="C26" t="str">
+        <v>eieren</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ingeblikte tomaten</v>
+        <v>frambozen</v>
       </c>
       <c r="B27" t="str">
-        <v>blik_tomaten</v>
+        <v>framboos</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>poedersuiker</v>
+        <v>gedroogde_gist</v>
       </c>
       <c r="B28" t="str">
-        <v>bloemsuiker</v>
+        <v>droge gist</v>
+      </c>
+      <c r="C28" t="str">
+        <v>droogzout</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>blauwe bes</v>
+        <v>gehakt</v>
       </c>
       <c r="B29" t="str">
-        <v>bosbessen</v>
+        <v>gehakt vlees</v>
+      </c>
+      <c r="C29" t="str">
+        <v>rundergehakt</v>
+      </c>
+      <c r="D29" t="str">
+        <v>varkensgehakt</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>blauwe bessen</v>
+        <v>gehakte_walnoten</v>
       </c>
       <c r="B30" t="str">
-        <v>bosbessen</v>
+        <v>gehakte noten</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>bosbes</v>
+        <v>gele_paprika</v>
       </c>
       <c r="B31" t="str">
-        <v>bosbessen</v>
+        <v>gele paprika</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>bouillon blokje</v>
+        <v>gember</v>
       </c>
       <c r="B32" t="str">
-        <v>bouillon</v>
+        <v>gemberpowder</v>
+      </c>
+      <c r="C32" t="str">
+        <v>verse gember</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>basterdsuiker</v>
+        <v>geraspte_kaas</v>
       </c>
       <c r="B33" t="str">
-        <v>bruine_suiker</v>
+        <v>geraspte kaas</v>
+      </c>
+      <c r="C33" t="str">
+        <v>gruyere</v>
+      </c>
+      <c r="D33" t="str">
+        <v>gruyère</v>
+      </c>
+      <c r="E33" t="str">
+        <v>kaas</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>bruine suiker</v>
+        <v>geraspte_wortelen</v>
       </c>
       <c r="B34" t="str">
-        <v>bruine_suiker</v>
+        <v>geraspte wortel</v>
+      </c>
+      <c r="C34" t="str">
+        <v>geraspte wortels</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>cassonade</v>
+        <v>gerookte_zalm</v>
       </c>
       <c r="B35" t="str">
-        <v>bruine_suiker</v>
+        <v>gerookte zalm</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>butternut squash</v>
+        <v>ghee</v>
       </c>
       <c r="B36" t="str">
-        <v>butternut</v>
+        <v>geklaarde boter</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ghee</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>pompoen</v>
+        <v>groene_asperges</v>
       </c>
       <c r="B37" t="str">
-        <v>butternut</v>
+        <v>asperge</v>
+      </c>
+      <c r="C37" t="str">
+        <v>asperges</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>cacao poeder</v>
+        <v>groentenbouillon</v>
       </c>
       <c r="B38" t="str">
-        <v>cacao</v>
+        <v>groentenbouillon</v>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>cacaopoeder</v>
+        <v>hagelslag</v>
       </c>
       <c r="B39" t="str">
-        <v>cacao</v>
+        <v>hagelslag</v>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>spaghetti</v>
+        <v>hazelnoten</v>
       </c>
       <c r="B40" t="str">
-        <v>cappelini</v>
+        <v>hazelnoot</v>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>champignon</v>
+        <v>honing</v>
       </c>
       <c r="B41" t="str">
-        <v>champignons</v>
+        <v>honing</v>
+      </c>
+      <c r="C41" t="str">
+        <v>vloeibare honing</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>paddenstoel</v>
+        <v>ijsbergsla</v>
       </c>
       <c r="B42" t="str">
-        <v>champignons</v>
+        <v>ijssla</v>
+      </c>
+      <c r="C42" t="str">
+        <v>sla</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>paddenstoelen</v>
+        <v>jalapenos</v>
       </c>
       <c r="B43" t="str">
-        <v>champignons</v>
+        <v>jalapeño</v>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>chili</v>
+        <v>kalkoenlapjes</v>
       </c>
       <c r="B44" t="str">
-        <v>chilipepers</v>
+        <v>kalkoen</v>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>chilivlokken</v>
+        <v>kerstomaatjes</v>
       </c>
       <c r="B45" t="str">
-        <v>chilipepers</v>
+        <v>cherry tomaten</v>
+      </c>
+      <c r="C45" t="str">
+        <v>cherrytomaatje</v>
+      </c>
+      <c r="D45" t="str">
+        <v>cherrytomaatjes</v>
+      </c>
+      <c r="E45" t="str">
+        <v>kerstomaat</v>
+      </c>
+      <c r="F45" t="str">
+        <v>kerstomaten</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>rode peper</v>
+        <v>kipdijfilet</v>
       </c>
       <c r="B46" t="str">
-        <v>chilipepers</v>
+        <v>kipdij</v>
+      </c>
+      <c r="C46" t="str">
+        <v>kipdijen</v>
+      </c>
+      <c r="D46" t="str">
+        <v>kippenboutenfilet</v>
+      </c>
+      <c r="E46" t="str">
+        <v>kippendijen</v>
+      </c>
+      <c r="F46" t="str">
+        <v>kippendijenfilet</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>melkchocolade</v>
+        <v>kipfilet</v>
       </c>
       <c r="B47" t="str">
-        <v>chocolade</v>
+        <v>kip</v>
+      </c>
+      <c r="C47" t="str">
+        <v>kippenborst</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>pure chocolade</v>
+        <v>kippenbouillon</v>
       </c>
       <c r="B48" t="str">
-        <v>chocolade</v>
+        <v>kippenbouillon</v>
+      </c>
+      <c r="C48" t="str">
+        <v/>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>citroensap</v>
+        <v>kippenkruiden</v>
       </c>
       <c r="B49" t="str">
-        <v>citroen</v>
+        <v>bbq kruiden</v>
+      </c>
+      <c r="C49" t="str">
+        <v>kippenkruiden</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>currypoeder</v>
+        <v>kippenworsten</v>
       </c>
       <c r="B50" t="str">
-        <v>curry</v>
+        <v>kippenworst</v>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ei</v>
+        <v>kipschnitzel</v>
       </c>
       <c r="B51" t="str">
-        <v>eieren_1</v>
+        <v>kippenschnitzel</v>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>eieren</v>
+        <v>kokosmelk</v>
       </c>
       <c r="B52" t="str">
-        <v>eieren_1</v>
+        <v>kokosmelk</v>
+      </c>
+      <c r="C52" t="str">
+        <v>kokosroom</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>framboos</v>
+        <v>kokosolie</v>
       </c>
       <c r="B53" t="str">
-        <v>frambozen</v>
+        <v>kokosolie</v>
+      </c>
+      <c r="C53" t="str">
+        <v>kokosvet</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>droge gist</v>
+        <v>komkommer</v>
       </c>
       <c r="B54" t="str">
-        <v>gedroogde_gist</v>
+        <v>komkommertje</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>droogzout</v>
+        <v>koriander</v>
       </c>
       <c r="B55" t="str">
-        <v>gedroogde_gist</v>
+        <v>verse koriander</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>gehakt vlees</v>
+        <v>lasagnevellen</v>
       </c>
       <c r="B56" t="str">
-        <v>gehakt</v>
+        <v>pasta</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>rundergehakt</v>
+        <v>laurier</v>
       </c>
       <c r="B57" t="str">
-        <v>gehakt</v>
+        <v>laurierblaadjes</v>
+      </c>
+      <c r="C57" t="str">
+        <v>laurierblad</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>varkensgehakt</v>
+        <v>limoen</v>
       </c>
       <c r="B58" t="str">
-        <v>gehakt</v>
+        <v>limoen</v>
+      </c>
+      <c r="C58" t="str">
+        <v>limoensap</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>gehakte noten</v>
+        <v>look</v>
       </c>
       <c r="B59" t="str">
-        <v>gehakte_walnoten</v>
+        <v>knoflook</v>
+      </c>
+      <c r="C59" t="str">
+        <v>knoflookteentje</v>
+      </c>
+      <c r="D59" t="str">
+        <v>knoflookteentjes</v>
+      </c>
+      <c r="E59" t="str">
+        <v>lookteentje</v>
+      </c>
+      <c r="F59" t="str">
+        <v>lookteentjes</v>
+      </c>
+      <c r="G59" t="str">
+        <v>teentje knoflook</v>
+      </c>
+      <c r="H59" t="str">
+        <v>teentjes knoflook</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>gele paprika</v>
+        <v>mais</v>
       </c>
       <c r="B60" t="str">
-        <v>gele_paprika</v>
+        <v>mais</v>
+      </c>
+      <c r="C60" t="str">
+        <v>maïs</v>
+      </c>
+      <c r="D60" t="str">
+        <v>maiskorrels</v>
+      </c>
+      <c r="E60" t="str">
+        <v>maïskorrels</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>gemberpowder</v>
+        <v>maizena</v>
       </c>
       <c r="B61" t="str">
-        <v>gember</v>
+        <v>maïzena</v>
+      </c>
+      <c r="C61" t="str">
+        <v>zetmeel</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>verse gember</v>
+        <v>mandarijnen</v>
       </c>
       <c r="B62" t="str">
-        <v>gember</v>
+        <v>mandarijn</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>geraspte kaas</v>
+        <v>mayonaise</v>
       </c>
       <c r="B63" t="str">
-        <v>geraspte_kaas</v>
+        <v>mayonnaise</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>gruyere</v>
+        <v>melk</v>
       </c>
       <c r="B64" t="str">
-        <v>geraspte_kaas</v>
+        <v>halfvolle melk</v>
+      </c>
+      <c r="C64" t="str">
+        <v>volle melk</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>gruyère</v>
+        <v>mini_komkommers</v>
       </c>
       <c r="B65" t="str">
-        <v>geraspte_kaas</v>
+        <v>mini komkommer</v>
+      </c>
+      <c r="C65" t="str">
+        <v>mini komkommers</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>kaas</v>
+        <v>mosterd</v>
       </c>
       <c r="B66" t="str">
-        <v>geraspte_kaas</v>
+        <v>dijonmmosterd</v>
+      </c>
+      <c r="C66" t="str">
+        <v>mosterd</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>geraspte wortel</v>
+        <v>mozarella</v>
       </c>
       <c r="B67" t="str">
-        <v>geraspte_wortelen</v>
+        <v>mozzarella</v>
+      </c>
+      <c r="C67" t="str">
+        <v>mozzarelle</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>geraspte wortels</v>
+        <v>munt</v>
       </c>
       <c r="B68" t="str">
-        <v>geraspte_wortelen</v>
+        <v>verse munt</v>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>gerookte zalm</v>
+        <v>olijfolie</v>
       </c>
       <c r="B69" t="str">
-        <v>gerookte_zalm</v>
+        <v>extra vergine olijfolie</v>
+      </c>
+      <c r="C69" t="str">
+        <v>olijfolie extra vierge</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>geklaarde boter</v>
+        <v>paksoi</v>
       </c>
       <c r="B70" t="str">
-        <v>ghee</v>
+        <v>paksoy</v>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ghee</v>
+        <v>paneermeel</v>
       </c>
       <c r="B71" t="str">
-        <v>ghee</v>
+        <v>broodkruim</v>
+      </c>
+      <c r="C71" t="str">
+        <v>broodkruimels</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>asperge</v>
+        <v>paprika</v>
       </c>
       <c r="B72" t="str">
-        <v>groene_asperges</v>
+        <v>groene paprika</v>
+      </c>
+      <c r="C72" t="str">
+        <v>paprika</v>
+      </c>
+      <c r="D72" t="str">
+        <v>rode paprika</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>asperges</v>
+        <v>parmaham</v>
       </c>
       <c r="B73" t="str">
-        <v>groene_asperges</v>
+        <v>parma ham</v>
+      </c>
+      <c r="C73" t="str">
+        <v>rauwe ham</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>groentenbouillon</v>
+        <v>parmezaan</v>
       </c>
       <c r="B74" t="str">
-        <v>groentenbouillon</v>
+        <v>parmezaan kaas</v>
+      </c>
+      <c r="C74" t="str">
+        <v>parmezaankaas</v>
+      </c>
+      <c r="D74" t="str">
+        <v>parmezaanse kaas</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>hagelslag</v>
+        <v>passata</v>
       </c>
       <c r="B75" t="str">
-        <v>hagelslag</v>
+        <v>passata</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>hazelnoot</v>
+        <v>peren</v>
       </c>
       <c r="B76" t="str">
-        <v>hazelnoten</v>
+        <v>peer</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>honing</v>
+        <v>peterselie</v>
       </c>
       <c r="B77" t="str">
-        <v>honing</v>
+        <v>verse peterselie</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>vloeibare honing</v>
+        <v>pijpajuin</v>
       </c>
       <c r="B78" t="str">
-        <v>honing</v>
+        <v>bosui</v>
+      </c>
+      <c r="C78" t="str">
+        <v>bosuitje</v>
+      </c>
+      <c r="D78" t="str">
+        <v>bosuitjes</v>
+      </c>
+      <c r="E78" t="str">
+        <v>lente-ui</v>
+      </c>
+      <c r="F78" t="str">
+        <v>lenteui</v>
+      </c>
+      <c r="G78" t="str">
+        <v>lenteuitje</v>
+      </c>
+      <c r="H78" t="str">
+        <v>pijpajuintje</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>ijssla</v>
+        <v>platte_kaas</v>
       </c>
       <c r="B79" t="str">
-        <v>ijsbergsla</v>
+        <v>kwark</v>
+      </c>
+      <c r="C79" t="str">
+        <v>platte kaas</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sla</v>
+        <v>pudding_poeder</v>
       </c>
       <c r="B80" t="str">
-        <v>ijsbergsla</v>
+        <v>pudding</v>
+      </c>
+      <c r="C80" t="str">
+        <v>puddingpoeder</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jalapeño</v>
+        <v>radijsjes</v>
       </c>
       <c r="B81" t="str">
-        <v>jalapenos</v>
+        <v>radijs</v>
+      </c>
+      <c r="C81" t="str">
+        <v>radiJs</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>kalkoen</v>
+        <v>rijstpapier</v>
       </c>
       <c r="B82" t="str">
-        <v>kalkoenlapjes</v>
+        <v>rijstvellen</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>cherry tomaten</v>
+        <v>rode_ajuin</v>
       </c>
       <c r="B83" t="str">
-        <v>kerstomaatjes</v>
+        <v>rode ajuin</v>
+      </c>
+      <c r="C83" t="str">
+        <v>rode ui</v>
+      </c>
+      <c r="D83" t="str">
+        <v>rode uien</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>cherrytomaatje</v>
+        <v>rode_currypasta</v>
       </c>
       <c r="B84" t="str">
-        <v>kerstomaatjes</v>
+        <v>currypasta</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>cherrytomaatjes</v>
+        <v>rode_wijn</v>
       </c>
       <c r="B85" t="str">
-        <v>kerstomaatjes</v>
+        <v>rode wijn</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>kerstomaat</v>
+        <v>room</v>
       </c>
       <c r="B86" t="str">
-        <v>kerstomaatjes</v>
+        <v>room</v>
+      </c>
+      <c r="C86" t="str">
+        <v>slagroom</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>kerstomaten</v>
+        <v>rozemarijn</v>
       </c>
       <c r="B87" t="str">
-        <v>kerstomaatjes</v>
+        <v>verse rozemarijn</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>kipdij</v>
+        <v>rundsbouillon</v>
       </c>
       <c r="B88" t="str">
-        <v>kipdijfilet</v>
+        <v>runderbouillon</v>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>kipdijen</v>
+        <v>satekruiden</v>
       </c>
       <c r="B89" t="str">
-        <v>kipdijfilet</v>
+        <v>satékruiden</v>
+      </c>
+      <c r="C89" t="str">
+        <v>satésaus</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>kippenboutenfilet</v>
+        <v>scampis</v>
       </c>
       <c r="B90" t="str">
-        <v>kipdijfilet</v>
+        <v>oester</v>
+      </c>
+      <c r="C90" t="str">
+        <v>scampi</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>kippendijen</v>
+        <v>selder</v>
       </c>
       <c r="B91" t="str">
-        <v>kipdijfilet</v>
+        <v>selderie</v>
+      </c>
+      <c r="C91" t="str">
+        <v>selderij</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>kippendijenfilet</v>
+        <v>sesamolie</v>
       </c>
       <c r="B92" t="str">
-        <v>kipdijfilet</v>
+        <v>sesamolie</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>kip</v>
+        <v>sjalotten</v>
       </c>
       <c r="B93" t="str">
-        <v>kipfilet</v>
+        <v>sjalot</v>
+      </c>
+      <c r="C93" t="str">
+        <v>sjalotje</v>
+      </c>
+      <c r="D93" t="str">
+        <v>sjalotjes</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>kippenborst</v>
+        <v>sojasaus</v>
       </c>
       <c r="B94" t="str">
-        <v>kipfilet</v>
+        <v>soja saus</v>
+      </c>
+      <c r="C94" t="str">
+        <v>sojasaus</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>kippenbouillon</v>
+        <v>spekblokjes</v>
       </c>
       <c r="B95" t="str">
-        <v>kippenbouillon</v>
+        <v>lardons</v>
+      </c>
+      <c r="C95" t="str">
+        <v>spekblokje</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>bbq kruiden</v>
+        <v>speltbloem</v>
       </c>
       <c r="B96" t="str">
-        <v>kippenkruiden</v>
+        <v>speltmeel</v>
+      </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>kippenkruiden</v>
+        <v>suiker</v>
       </c>
       <c r="B97" t="str">
-        <v>kippenkruiden</v>
+        <v>fijne suiker</v>
+      </c>
+      <c r="C97" t="str">
+        <v>kristalsuiker</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>kippenworst</v>
+        <v>suikerklontjes</v>
       </c>
       <c r="B98" t="str">
-        <v>kippenworsten</v>
+        <v>suikerklontje</v>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>kippenschnitzel</v>
+        <v>tijm</v>
       </c>
       <c r="B99" t="str">
-        <v>kipschnitzel</v>
+        <v>verse tijm</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>kokosmelk</v>
+        <v>tomaten</v>
       </c>
       <c r="B100" t="str">
-        <v>kokosmelk</v>
+        <v>tomaat</v>
+      </c>
+      <c r="C100" t="str">
+        <v>tomaatje</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>kokosroom</v>
+        <v>tomaten_uit_blik</v>
       </c>
       <c r="B101" t="str">
-        <v>kokosmelk</v>
+        <v>tomaten uit blik</v>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>kokosolie</v>
+        <v>tomatenblokjes</v>
       </c>
       <c r="B102" t="str">
-        <v>kokosolie</v>
+        <v>tomatenblokjes</v>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>kokosvet</v>
+        <v>tomatenpuree</v>
       </c>
       <c r="B103" t="str">
-        <v>kokosolie</v>
+        <v>geconcentreerde tomatenpuree</v>
+      </c>
+      <c r="C103" t="str">
+        <v>tomatenpuree</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>komkommertje</v>
+        <v>vanillearoma</v>
       </c>
       <c r="B104" t="str">
-        <v>komkommer</v>
+        <v>vanille extract</v>
+      </c>
+      <c r="C104" t="str">
+        <v>vanilleextract</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>verse koriander</v>
+        <v>vanillestokjes</v>
       </c>
       <c r="B105" t="str">
-        <v>koriander</v>
+        <v>vanillestokje</v>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>pasta</v>
+        <v>verse_gist</v>
       </c>
       <c r="B106" t="str">
-        <v>lasagnevellen</v>
+        <v>gist</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>laurierblaadjes</v>
+        <v>visbouillon</v>
       </c>
       <c r="B107" t="str">
-        <v>laurier</v>
+        <v>visbouillon</v>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>laurierblad</v>
+        <v>vleesbouillon</v>
       </c>
       <c r="B108" t="str">
-        <v>laurier</v>
+        <v>vleesbouillon</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>limoen</v>
+        <v>walnoten</v>
       </c>
       <c r="B109" t="str">
-        <v>limoen</v>
+        <v>walnoot</v>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>limoensap</v>
+        <v>witloof</v>
       </c>
       <c r="B110" t="str">
-        <v>limoen</v>
+        <v>witlof</v>
+      </c>
+      <c r="C110" t="str">
+        <v>witloof</v>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>knoflook</v>
+        <v>witte_wijn</v>
       </c>
       <c r="B111" t="str">
-        <v>look</v>
+        <v>witte wijn</v>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>knoflookteentje</v>
+        <v>wortelen</v>
       </c>
       <c r="B112" t="str">
-        <v>look</v>
+        <v>peen</v>
+      </c>
+      <c r="C112" t="str">
+        <v>penen</v>
+      </c>
+      <c r="D112" t="str">
+        <v>wortel</v>
+      </c>
+      <c r="E112" t="str">
+        <v>wortels</v>
+      </c>
+      <c r="F112" t="str">
+        <v>worteltje</v>
+      </c>
+      <c r="G112" t="str">
+        <v>worteltjes</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>knoflookteentjes</v>
+        <v>wraps</v>
       </c>
       <c r="B113" t="str">
-        <v>look</v>
+        <v>tortilla</v>
+      </c>
+      <c r="C113" t="str">
+        <v>wraps</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>lookteentje</v>
+        <v>yoghurt</v>
       </c>
       <c r="B114" t="str">
-        <v>look</v>
+        <v>Griekse yoghurt</v>
+      </c>
+      <c r="C114" t="str">
+        <v>yoghurt</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>lookteentjes</v>
+        <v>zalm</v>
       </c>
       <c r="B115" t="str">
-        <v>look</v>
+        <v>zalm filet</v>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>teentje knoflook</v>
+        <v>zelfrijzend_bakmeel</v>
       </c>
       <c r="B116" t="str">
-        <v>look</v>
+        <v>bloem</v>
+      </c>
+      <c r="C116" t="str">
+        <v>patentbloem</v>
+      </c>
+      <c r="D116" t="str">
+        <v>tarwebloem</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>teentjes knoflook</v>
+        <v>zilveruitjes</v>
       </c>
       <c r="B117" t="str">
-        <v>look</v>
+        <v>kappertje</v>
+      </c>
+      <c r="C117" t="str">
+        <v>zilverui</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>mais</v>
+        <v>zoete_aardappelen</v>
       </c>
       <c r="B118" t="str">
-        <v>mais</v>
+        <v>bataat</v>
+      </c>
+      <c r="C118" t="str">
+        <v>zoete aardappel</v>
+      </c>
+      <c r="D118" t="str">
+        <v>zoete aardappels</v>
+      </c>
+      <c r="E118" t="str">
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>maïs</v>
+        <v>zonnebloemolie</v>
       </c>
       <c r="B119" t="str">
-        <v>mais</v>
+        <v>plantaardige olie</v>
+      </c>
+      <c r="C119" t="str">
+        <v>zonnebloem olie</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>maiskorrels</v>
+        <v>zure_room</v>
       </c>
       <c r="B120" t="str">
-        <v>mais</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>maïskorrels</v>
-      </c>
-      <c r="B121" t="str">
-        <v>mais</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>maïzena</v>
-      </c>
-      <c r="B122" t="str">
-        <v>maizena</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>zetmeel</v>
-      </c>
-      <c r="B123" t="str">
-        <v>maizena</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>mandarijn</v>
-      </c>
-      <c r="B124" t="str">
-        <v>mandarijnen</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>mayonnaise</v>
-      </c>
-      <c r="B125" t="str">
-        <v>mayonaise</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>halfvolle melk</v>
-      </c>
-      <c r="B126" t="str">
-        <v>melk</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>volle melk</v>
-      </c>
-      <c r="B127" t="str">
-        <v>melk</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>mini komkommer</v>
-      </c>
-      <c r="B128" t="str">
-        <v>mini_komkommers</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>mini komkommers</v>
-      </c>
-      <c r="B129" t="str">
-        <v>mini_komkommers</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>dijonmmosterd</v>
-      </c>
-      <c r="B130" t="str">
-        <v>mosterd</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>mosterd</v>
-      </c>
-      <c r="B131" t="str">
-        <v>mosterd</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>mozzarella</v>
-      </c>
-      <c r="B132" t="str">
-        <v>mozarella</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>mozzarelle</v>
-      </c>
-      <c r="B133" t="str">
-        <v>mozarella</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>verse munt</v>
-      </c>
-      <c r="B134" t="str">
-        <v>munt</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>extra vergine olijfolie</v>
-      </c>
-      <c r="B135" t="str">
-        <v>olijfolie</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>olijfolie extra vierge</v>
-      </c>
-      <c r="B136" t="str">
-        <v>olijfolie</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>paksoy</v>
-      </c>
-      <c r="B137" t="str">
-        <v>paksoi</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>broodkruim</v>
-      </c>
-      <c r="B138" t="str">
-        <v>paneermeel</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>broodkruimels</v>
-      </c>
-      <c r="B139" t="str">
-        <v>paneermeel</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>groene paprika</v>
-      </c>
-      <c r="B140" t="str">
-        <v>paprika</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>paprika</v>
-      </c>
-      <c r="B141" t="str">
-        <v>paprika</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>rode paprika</v>
-      </c>
-      <c r="B142" t="str">
-        <v>paprika</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>parma ham</v>
-      </c>
-      <c r="B143" t="str">
-        <v>parmaham</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>rauwe ham</v>
-      </c>
-      <c r="B144" t="str">
-        <v>parmaham</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>parmezaan kaas</v>
-      </c>
-      <c r="B145" t="str">
-        <v>parmezaan</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>parmezaankaas</v>
-      </c>
-      <c r="B146" t="str">
-        <v>parmezaan</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>parmezaanse kaas</v>
-      </c>
-      <c r="B147" t="str">
-        <v>parmezaan</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>passata</v>
-      </c>
-      <c r="B148" t="str">
-        <v>passata</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>peer</v>
-      </c>
-      <c r="B149" t="str">
-        <v>peren</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>verse peterselie</v>
-      </c>
-      <c r="B150" t="str">
-        <v>peterselie</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>bosui</v>
-      </c>
-      <c r="B151" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>bosuitje</v>
-      </c>
-      <c r="B152" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>bosuitjes</v>
-      </c>
-      <c r="B153" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>lente-ui</v>
-      </c>
-      <c r="B154" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>lenteui</v>
-      </c>
-      <c r="B155" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>lenteuitje</v>
-      </c>
-      <c r="B156" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>pijpajuintje</v>
-      </c>
-      <c r="B157" t="str">
-        <v>pijpajuin</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>kwark</v>
-      </c>
-      <c r="B158" t="str">
-        <v>platte_kaas</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>platte kaas</v>
-      </c>
-      <c r="B159" t="str">
-        <v>platte_kaas</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>pudding</v>
-      </c>
-      <c r="B160" t="str">
-        <v>pudding_poeder</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>puddingpoeder</v>
-      </c>
-      <c r="B161" t="str">
-        <v>pudding_poeder</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>radijs</v>
-      </c>
-      <c r="B162" t="str">
-        <v>radijsjes</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>radiJs</v>
-      </c>
-      <c r="B163" t="str">
-        <v>radijsjes</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>rijstvellen</v>
-      </c>
-      <c r="B164" t="str">
-        <v>rijstpapier</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>rode ajuin</v>
-      </c>
-      <c r="B165" t="str">
-        <v>rode_ajuin</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>rode ui</v>
-      </c>
-      <c r="B166" t="str">
-        <v>rode_ajuin</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>rode uien</v>
-      </c>
-      <c r="B167" t="str">
-        <v>rode_ajuin</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>currypasta</v>
-      </c>
-      <c r="B168" t="str">
-        <v>rode_currypasta</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>rode wijn</v>
-      </c>
-      <c r="B169" t="str">
-        <v>rode_wijn</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>room</v>
-      </c>
-      <c r="B170" t="str">
-        <v>room</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>slagroom</v>
-      </c>
-      <c r="B171" t="str">
-        <v>room</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>verse rozemarijn</v>
-      </c>
-      <c r="B172" t="str">
-        <v>rozemarijn</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>runderbouillon</v>
-      </c>
-      <c r="B173" t="str">
-        <v>rundsbouillon</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>satékruiden</v>
-      </c>
-      <c r="B174" t="str">
-        <v>satekruiden</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>satésaus</v>
-      </c>
-      <c r="B175" t="str">
-        <v>satekruiden</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>oester</v>
-      </c>
-      <c r="B176" t="str">
-        <v>scampis</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>scampi</v>
-      </c>
-      <c r="B177" t="str">
-        <v>scampis</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>selderie</v>
-      </c>
-      <c r="B178" t="str">
-        <v>selder</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>selderij</v>
-      </c>
-      <c r="B179" t="str">
-        <v>selder</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>sesamolie</v>
-      </c>
-      <c r="B180" t="str">
-        <v>sesamolie</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>sjalot</v>
-      </c>
-      <c r="B181" t="str">
-        <v>sjalotten</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>sjalotje</v>
-      </c>
-      <c r="B182" t="str">
-        <v>sjalotten</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>sjalotjes</v>
-      </c>
-      <c r="B183" t="str">
-        <v>sjalotten</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>soja saus</v>
-      </c>
-      <c r="B184" t="str">
-        <v>sojasaus</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>sojasaus</v>
-      </c>
-      <c r="B185" t="str">
-        <v>sojasaus</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>lardons</v>
-      </c>
-      <c r="B186" t="str">
-        <v>spekblokjes</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>spekblokje</v>
-      </c>
-      <c r="B187" t="str">
-        <v>spekblokjes</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>speltmeel</v>
-      </c>
-      <c r="B188" t="str">
-        <v>speltbloem</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>fijne suiker</v>
-      </c>
-      <c r="B189" t="str">
-        <v>suiker</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>kristalsuiker</v>
-      </c>
-      <c r="B190" t="str">
-        <v>suiker</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>suikerklontje</v>
-      </c>
-      <c r="B191" t="str">
-        <v>suikerklontjes</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>verse tijm</v>
-      </c>
-      <c r="B192" t="str">
-        <v>tijm</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>tomaat</v>
-      </c>
-      <c r="B193" t="str">
-        <v>tomaten</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>tomaatje</v>
-      </c>
-      <c r="B194" t="str">
-        <v>tomaten</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>tomaten uit blik</v>
-      </c>
-      <c r="B195" t="str">
-        <v>tomaten_uit_blik</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>tomatenblokjes</v>
-      </c>
-      <c r="B196" t="str">
-        <v>tomatenblokjes</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>geconcentreerde tomatenpuree</v>
-      </c>
-      <c r="B197" t="str">
-        <v>tomatenpuree</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>tomatenpuree</v>
-      </c>
-      <c r="B198" t="str">
-        <v>tomatenpuree</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>vanille extract</v>
-      </c>
-      <c r="B199" t="str">
-        <v>vanillearoma</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>vanilleextract</v>
-      </c>
-      <c r="B200" t="str">
-        <v>vanillearoma</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>vanillestokje</v>
-      </c>
-      <c r="B201" t="str">
-        <v>vanillestokjes</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>gist</v>
-      </c>
-      <c r="B202" t="str">
-        <v>verse_gist</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>visbouillon</v>
-      </c>
-      <c r="B203" t="str">
-        <v>visbouillon</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>vleesbouillon</v>
-      </c>
-      <c r="B204" t="str">
-        <v>vleesbouillon</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>walnoot</v>
-      </c>
-      <c r="B205" t="str">
-        <v>walnoten</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>witlof</v>
-      </c>
-      <c r="B206" t="str">
-        <v>witloof</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>witloof</v>
-      </c>
-      <c r="B207" t="str">
-        <v>witloof</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>witte wijn</v>
-      </c>
-      <c r="B208" t="str">
-        <v>witte_wijn</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>peen</v>
-      </c>
-      <c r="B209" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>penen</v>
-      </c>
-      <c r="B210" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>wortel</v>
-      </c>
-      <c r="B211" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>wortels</v>
-      </c>
-      <c r="B212" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>worteltje</v>
-      </c>
-      <c r="B213" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>worteltjes</v>
-      </c>
-      <c r="B214" t="str">
-        <v>wortelen</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>tortilla</v>
-      </c>
-      <c r="B215" t="str">
-        <v>wraps</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>wraps</v>
-      </c>
-      <c r="B216" t="str">
-        <v>wraps</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Griekse yoghurt</v>
-      </c>
-      <c r="B217" t="str">
-        <v>yoghurt</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>yoghurt</v>
-      </c>
-      <c r="B218" t="str">
-        <v>yoghurt</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>zalm filet</v>
-      </c>
-      <c r="B219" t="str">
-        <v>zalm</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>bloem</v>
-      </c>
-      <c r="B220" t="str">
-        <v>zelfrijzend_bakmeel</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>patentbloem</v>
-      </c>
-      <c r="B221" t="str">
-        <v>zelfrijzend_bakmeel</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>tarwebloem</v>
-      </c>
-      <c r="B222" t="str">
-        <v>zelfrijzend_bakmeel</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>kappertje</v>
-      </c>
-      <c r="B223" t="str">
-        <v>zilveruitjes</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>zilverui</v>
-      </c>
-      <c r="B224" t="str">
-        <v>zilveruitjes</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>bataat</v>
-      </c>
-      <c r="B225" t="str">
-        <v>zoete_aardappelen</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>zoete aardappel</v>
-      </c>
-      <c r="B226" t="str">
-        <v>zoete_aardappelen</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>zoete aardappels</v>
-      </c>
-      <c r="B227" t="str">
-        <v>zoete_aardappelen</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>plantaardige olie</v>
-      </c>
-      <c r="B228" t="str">
-        <v>zonnebloemolie</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>zonnebloem olie</v>
-      </c>
-      <c r="B229" t="str">
-        <v>zonnebloemolie</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
         <v>zure room</v>
       </c>
-      <c r="B230" t="str">
-        <v>zure_room</v>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B230"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I120"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/images/items/ingredienten_categorieen.xlsx
+++ b/public/images/items/ingredienten_categorieen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristoflesaffre/Downloads/ShoppingList/public/images/items/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDFCB3C2-1DAB-4A43-A1BA-33678E0F3BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CD2604-FFC0-CA45-B59F-935B7448D7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="515">
   <si>
     <t>Categorie</t>
   </si>
@@ -1568,6 +1568,9 @@
   </si>
   <si>
     <t>kruiden</t>
+  </si>
+  <si>
+    <t>bou</t>
   </si>
 </sst>
 </file>
@@ -5393,7 +5396,9 @@
       <c r="B48" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="38"/>
+      <c r="C48" s="38" t="s">
+        <v>514</v>
+      </c>
       <c r="D48" s="38"/>
       <c r="E48" s="38"/>
       <c r="F48" s="38"/>

--- a/public/images/items/ingredienten_categorieen.xlsx
+++ b/public/images/items/ingredienten_categorieen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kristoflesaffre/Downloads/ShoppingList/public/images/items/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BFBC51-05C1-0B4B-A9E8-F69B7ED34734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A1E7E-C799-A441-B522-A1169A44ECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1661" uniqueCount="1055">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="1048">
   <si>
     <t>Afbeelding (png / slug)</t>
   </si>
@@ -607,9 +607,6 @@
     <t>rauwe rundvlees</t>
   </si>
   <si>
-    <t>carpaccio di manzo</t>
-  </si>
-  <si>
     <t>cecemel</t>
   </si>
   <si>
@@ -694,9 +691,6 @@
     <t>snack</t>
   </si>
   <si>
-    <t>crispy</t>
-  </si>
-  <si>
     <t>chocolade</t>
   </si>
   <si>
@@ -730,9 +724,6 @@
     <t>chocolade tablet</t>
   </si>
   <si>
-    <t>couverture</t>
-  </si>
-  <si>
     <t>chocoladedruppels</t>
   </si>
   <si>
@@ -844,9 +835,6 @@
     <t>afvoerreiniger</t>
   </si>
   <si>
-    <t>drain opener</t>
-  </si>
-  <si>
     <t>diepvrieswortels</t>
   </si>
   <si>
@@ -1000,9 +988,6 @@
     <t>frituurolie</t>
   </si>
   <si>
-    <t>palmvet</t>
-  </si>
-  <si>
     <t>bakvet</t>
   </si>
   <si>
@@ -1177,21 +1162,9 @@
     <t>mechels bier</t>
   </si>
   <si>
-    <t>het anker</t>
-  </si>
-  <si>
     <t>green_tea</t>
   </si>
   <si>
-    <t>groene thee</t>
-  </si>
-  <si>
-    <t>matcha</t>
-  </si>
-  <si>
-    <t>japanese green tea</t>
-  </si>
-  <si>
     <t>griekse_yoghurt</t>
   </si>
   <si>
@@ -1246,12 +1219,6 @@
     <t>hamburger</t>
   </si>
   <si>
-    <t>hamburgerbroodje</t>
-  </si>
-  <si>
-    <t>burgerbroodje</t>
-  </si>
-  <si>
     <t>burger</t>
   </si>
   <si>
@@ -3191,6 +3158,18 @@
   </si>
   <si>
     <t>rode vruchtenthee</t>
+  </si>
+  <si>
+    <t>zoute chips</t>
+  </si>
+  <si>
+    <t>bier</t>
+  </si>
+  <si>
+    <t>thee</t>
+  </si>
+  <si>
+    <t>olie</t>
   </si>
 </sst>
 </file>
@@ -4068,87 +4047,87 @@
   <sheetData>
     <row r="1" spans="1:1" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
     </row>
   </sheetData>
@@ -4170,10 +4149,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4181,7 +4160,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4189,7 +4168,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4197,7 +4176,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4205,7 +4184,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4213,7 +4192,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4221,7 +4200,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4229,7 +4208,7 @@
         <v>29</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4237,7 +4216,7 @@
         <v>36</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4245,7 +4224,7 @@
         <v>39</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4253,7 +4232,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4261,7 +4240,7 @@
         <v>50</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4269,7 +4248,7 @@
         <v>54</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4277,7 +4256,7 @@
         <v>58</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4285,7 +4264,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4293,7 +4272,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4301,7 +4280,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4309,7 +4288,7 @@
         <v>77</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4317,7 +4296,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4325,7 +4304,7 @@
         <v>81</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4333,7 +4312,7 @@
         <v>84</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4341,7 +4320,7 @@
         <v>89</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4349,7 +4328,7 @@
         <v>93</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4357,7 +4336,7 @@
         <v>95</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4365,7 +4344,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4373,7 +4352,7 @@
         <v>99</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4381,7 +4360,7 @@
         <v>104</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4389,7 +4368,7 @@
         <v>108</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4397,7 +4376,7 @@
         <v>112</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4405,7 +4384,7 @@
         <v>116</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4413,7 +4392,7 @@
         <v>120</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4421,7 +4400,7 @@
         <v>122</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4429,7 +4408,7 @@
         <v>125</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4437,7 +4416,7 @@
         <v>129</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4445,7 +4424,7 @@
         <v>132</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4453,7 +4432,7 @@
         <v>133</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4461,7 +4440,7 @@
         <v>136</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4469,7 +4448,7 @@
         <v>140</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4477,7 +4456,7 @@
         <v>144</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4485,7 +4464,7 @@
         <v>149</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4493,7 +4472,7 @@
         <v>158</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4501,7 +4480,7 @@
         <v>162</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4509,7 +4488,7 @@
         <v>166</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4517,7 +4496,7 @@
         <v>170</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4525,7 +4504,7 @@
         <v>175</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4533,7 +4512,7 @@
         <v>179</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4541,7 +4520,7 @@
         <v>180</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4549,7 +4528,7 @@
         <v>183</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4557,1775 +4536,1775 @@
         <v>190</v>
       </c>
       <c r="B49" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B55" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B56" s="32" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="20" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="22" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="20" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="22" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="22" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="20" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="22" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B67" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="20" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="22" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="20" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="22" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="20" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B72" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="22" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="20" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="22" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="22" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="20" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="22" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="20" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="22" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B81" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="20" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="22" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B83" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="20" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B84" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="22" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B85" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="20" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="22" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="20" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="22" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="20" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="22" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="20" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="22" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="20" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B94" s="30" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="22" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="20" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="22" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B97" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="20" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="22" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B99" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="20" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B100" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="22" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B101" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="20" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B102" s="36" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="22" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="20" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="22" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B105" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="20" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="22" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="20" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="22" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="20" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B110" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="22" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="20" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B112" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="22" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B113" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="20" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="22" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B115" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="20" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="22" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="B117" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="20" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="22" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B119" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="20" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="22" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="B121" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="20" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="22" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="20" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="B124" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="22" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="20" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B126" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="22" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="20" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B128" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="22" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="20" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="22" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="20" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B132" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="22" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="B133" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="20" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="B134" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="22" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="B135" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="20" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="B136" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="22" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="B137" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="20" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="B138" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="22" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="B139" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="20" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B140" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="22" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="B141" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="20" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B142" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="22" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="20" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="22" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="20" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="B146" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="22" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B147" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="20" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="B148" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="22" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="B149" s="30" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="20" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="B150" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="22" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B151" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="20" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B152" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="22" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="B153" s="32" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="20" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B154" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="22" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B155" s="36" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="20" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="22" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="B157" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="20" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B158" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="22" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="B159" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="20" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B160" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="22" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="B161" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="20" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B162" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="22" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="20" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="B164" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="22" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="B165" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="20" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="B166" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="22" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="B167" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="20" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B168" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="22" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B169" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="20" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="B170" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="22" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B171" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="20" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="B172" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="22" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="B173" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="20" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="B174" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="22" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="B175" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="20" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="B176" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="22" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="20" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="B178" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="22" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B179" s="24" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="20" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="22" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="B181" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="20" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B182" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="22" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="B183" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="20" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="B184" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="22" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="B185" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="20" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="B186" s="33" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="22" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="B187" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="20" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="B188" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="22" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B189" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="20" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B190" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="22" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="B191" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="20" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B192" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="22" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="B193" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="20" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="B194" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="22" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="B195" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="20" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="B196" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="22" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="20" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="B198" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="22" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="B199" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="20" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="B200" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="22" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="B201" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="20" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B202" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="22" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B203" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="20" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="B204" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="22" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="B205" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="20" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B206" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="22" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="B207" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="20" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="B208" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="22" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="B209" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="20" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="B210" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="22" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="B211" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="20" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="B212" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="22" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B213" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="20" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="B214" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="22" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="B215" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="20" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="B216" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="22" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="B217" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="20" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="B218" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="22" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B219" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="20" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="B220" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="22" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="B221" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="20" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="B222" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="22" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="B223" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="20" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="B224" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="22" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="B225" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="20" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="B226" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="22" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="B227" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="20" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="B228" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="22" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B229" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="20" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="B230" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="22" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B231" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="20" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="22" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="20" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="B234" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="22" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="B235" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="20" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="B236" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="22" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B237" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="20" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B238" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="22" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="B239" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="20" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="B240" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="22" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="B241" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="20" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="B242" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="22" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B243" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="20" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="B244" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="22" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="B245" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="20" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="B246" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="22" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="B247" s="32" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="20" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="B248" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="22" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="B249" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="20" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="B250" s="34" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" s="22" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" s="20" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" s="22" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B253" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" s="20" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="B254" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" s="22" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B255" s="31" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" s="20" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B256" s="28" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" s="22" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="B257" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="20" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B258" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" s="22" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B259" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" s="20" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="B260" s="25" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="22" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B261" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" s="20" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="B262" s="35" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" s="22" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="B263" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="20" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="B264" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" s="22" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="B265" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" s="20" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="B266" s="23" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="22" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
       <c r="B267" s="29" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" s="20" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="B268" s="21" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" s="22" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
       <c r="B269" s="27" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="20" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="B270" s="26" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>
@@ -6429,10 +6408,10 @@
         <v>20</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
       <c r="H4" s="39" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="I4" s="39"/>
     </row>
@@ -6444,7 +6423,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="41"/>
@@ -6551,7 +6530,7 @@
         <v>42</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
       <c r="F10" s="39"/>
       <c r="G10" s="39"/>
@@ -6587,7 +6566,7 @@
         <v>49</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>1052</v>
+        <v>1041</v>
       </c>
       <c r="D12" s="39"/>
       <c r="E12" s="39"/>
@@ -6675,7 +6654,7 @@
         <v>68</v>
       </c>
       <c r="G16" s="39" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
       <c r="H16" s="39"/>
       <c r="I16" s="39"/>
@@ -7115,7 +7094,7 @@
         <v>148</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
       <c r="G41" s="41"/>
       <c r="H41" s="41"/>
@@ -7316,7 +7295,9 @@
       <c r="B52" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="39"/>
+      <c r="C52" s="39" t="s">
+        <v>508</v>
+      </c>
       <c r="D52" s="39"/>
       <c r="E52" s="39"/>
       <c r="F52" s="39"/>
@@ -7334,9 +7315,7 @@
       <c r="C53" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>193</v>
-      </c>
+      <c r="D53" s="22"/>
       <c r="E53" s="41"/>
       <c r="F53" s="41"/>
       <c r="G53" s="41"/>
@@ -7345,16 +7324,16 @@
     </row>
     <row r="54" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="B54" s="38" t="s">
+      <c r="C54" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C54" s="38" t="s">
+      <c r="D54" s="38" t="s">
         <v>196</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>197</v>
       </c>
       <c r="E54" s="39"/>
       <c r="F54" s="39"/>
@@ -7364,19 +7343,19 @@
     </row>
     <row r="55" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="B55" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="C55" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="D55" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="D55" s="22" t="s">
+      <c r="E55" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>202</v>
       </c>
       <c r="F55" s="41"/>
       <c r="G55" s="41"/>
@@ -7385,16 +7364,16 @@
     </row>
     <row r="56" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="B56" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="B56" s="38" t="s">
+      <c r="C56" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="D56" s="38" t="s">
         <v>205</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>206</v>
       </c>
       <c r="E56" s="39"/>
       <c r="F56" s="39"/>
@@ -7404,18 +7383,20 @@
     </row>
     <row r="57" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="B57" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="B57" s="22" t="s">
+      <c r="C57" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="D57" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="D57" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="E57" s="41"/>
+      <c r="E57" s="41" t="s">
+        <v>351</v>
+      </c>
       <c r="F57" s="41"/>
       <c r="G57" s="41"/>
       <c r="H57" s="41"/>
@@ -7423,13 +7404,13 @@
     </row>
     <row r="58" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="B58" s="38" t="s">
+      <c r="C58" s="38" t="s">
         <v>212</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>213</v>
       </c>
       <c r="D58" s="39"/>
       <c r="E58" s="39"/>
@@ -7440,19 +7421,19 @@
     </row>
     <row r="59" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="B59" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="B59" s="22" t="s">
+      <c r="C59" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="C59" s="22" t="s">
+      <c r="D59" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="E59" s="22" t="s">
         <v>217</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>218</v>
       </c>
       <c r="F59" s="41"/>
       <c r="G59" s="41"/>
@@ -7461,16 +7442,16 @@
     </row>
     <row r="60" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="B60" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="B60" s="38" t="s">
+      <c r="C60" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="C60" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="D60" s="38" t="s">
-        <v>222</v>
+      <c r="D60" s="42" t="s">
+        <v>1044</v>
       </c>
       <c r="E60" s="39"/>
       <c r="F60" s="39"/>
@@ -7480,13 +7461,13 @@
     </row>
     <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="B61" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="C61" s="22" t="s">
-        <v>225</v>
       </c>
       <c r="D61" s="41"/>
       <c r="E61" s="41"/>
@@ -7497,16 +7478,16 @@
     </row>
     <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C62" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="B62" s="38" t="s">
+      <c r="D62" s="38" t="s">
         <v>227</v>
-      </c>
-      <c r="C62" s="38" t="s">
-        <v>228</v>
-      </c>
-      <c r="D62" s="38" t="s">
-        <v>229</v>
       </c>
       <c r="E62" s="39"/>
       <c r="F62" s="39"/>
@@ -7516,20 +7497,18 @@
     </row>
     <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="40" t="s">
+        <v>228</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="C63" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="22" t="s">
+      <c r="D63" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="C63" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="D63" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="E63" s="22" t="s">
-        <v>234</v>
-      </c>
+      <c r="E63" s="22"/>
       <c r="F63" s="41"/>
       <c r="G63" s="41"/>
       <c r="H63" s="41"/>
@@ -7537,19 +7516,19 @@
     </row>
     <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>233</v>
+      </c>
+      <c r="C64" s="38" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="B64" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="C64" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D64" s="38" t="s">
-        <v>238</v>
-      </c>
       <c r="E64" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F64" s="39"/>
       <c r="G64" s="39"/>
@@ -7558,16 +7537,16 @@
     </row>
     <row r="65" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="40" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="D65" s="22" t="s">
-        <v>242</v>
+        <v>238</v>
+      </c>
+      <c r="D65" s="43" t="s">
+        <v>1045</v>
       </c>
       <c r="E65" s="41"/>
       <c r="F65" s="41"/>
@@ -7577,10 +7556,10 @@
     </row>
     <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C66" s="39"/>
       <c r="D66" s="39"/>
@@ -7592,19 +7571,19 @@
     </row>
     <row r="67" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D67" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="22" t="s">
+      <c r="E67" s="22" t="s">
         <v>246</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>249</v>
       </c>
       <c r="F67" s="41"/>
       <c r="G67" s="41"/>
@@ -7613,16 +7592,16 @@
     </row>
     <row r="68" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="C68" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="D68" s="38" t="s">
         <v>250</v>
-      </c>
-      <c r="B68" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="C68" s="38" t="s">
-        <v>252</v>
-      </c>
-      <c r="D68" s="38" t="s">
-        <v>253</v>
       </c>
       <c r="E68" s="39"/>
       <c r="F68" s="39"/>
@@ -7632,18 +7611,20 @@
     </row>
     <row r="69" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D69" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="B69" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="E69" s="41"/>
+      <c r="E69" s="41" t="s">
+        <v>1045</v>
+      </c>
       <c r="F69" s="41"/>
       <c r="G69" s="41"/>
       <c r="H69" s="41"/>
@@ -7651,16 +7632,16 @@
     </row>
     <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="B70" s="38" t="s">
+        <v>256</v>
+      </c>
+      <c r="C70" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="D70" s="38" t="s">
         <v>258</v>
-      </c>
-      <c r="B70" s="38" t="s">
-        <v>259</v>
-      </c>
-      <c r="C70" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="D70" s="38" t="s">
-        <v>261</v>
       </c>
       <c r="E70" s="39"/>
       <c r="F70" s="39"/>
@@ -7670,10 +7651,10 @@
     </row>
     <row r="71" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="40" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C71" s="41"/>
       <c r="D71" s="41"/>
@@ -7685,19 +7666,19 @@
     </row>
     <row r="72" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" s="38" t="s">
+        <v>262</v>
+      </c>
+      <c r="C72" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="D72" s="38" t="s">
         <v>264</v>
       </c>
-      <c r="B72" s="38" t="s">
+      <c r="E72" s="38" t="s">
         <v>265</v>
-      </c>
-      <c r="C72" s="38" t="s">
-        <v>266</v>
-      </c>
-      <c r="D72" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="E72" s="38" t="s">
-        <v>268</v>
       </c>
       <c r="F72" s="39"/>
       <c r="G72" s="39"/>
@@ -7706,17 +7687,15 @@
     </row>
     <row r="73" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="40" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>271</v>
-      </c>
-      <c r="D73" s="22" t="s">
-        <v>272</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="D73" s="22"/>
       <c r="E73" s="41"/>
       <c r="F73" s="41"/>
       <c r="G73" s="41"/>
@@ -7725,16 +7704,16 @@
     </row>
     <row r="74" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="37" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C74" s="38" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E74" s="39"/>
       <c r="F74" s="39"/>
@@ -7744,19 +7723,19 @@
     </row>
     <row r="75" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="E75" s="22" t="s">
         <v>277</v>
-      </c>
-      <c r="B75" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="D75" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="E75" s="22" t="s">
-        <v>281</v>
       </c>
       <c r="F75" s="41"/>
       <c r="G75" s="41"/>
@@ -7765,19 +7744,19 @@
     </row>
     <row r="76" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="37" t="s">
+        <v>278</v>
+      </c>
+      <c r="B76" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="C76" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="D76" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="E76" s="38" t="s">
         <v>282</v>
-      </c>
-      <c r="B76" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="C76" s="38" t="s">
-        <v>284</v>
-      </c>
-      <c r="D76" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="E76" s="38" t="s">
-        <v>286</v>
       </c>
       <c r="F76" s="39"/>
       <c r="G76" s="39"/>
@@ -7786,18 +7765,20 @@
     </row>
     <row r="77" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="40" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="E77" s="41"/>
+        <v>286</v>
+      </c>
+      <c r="E77" s="41" t="s">
+        <v>1046</v>
+      </c>
       <c r="F77" s="41"/>
       <c r="G77" s="41"/>
       <c r="H77" s="41"/>
@@ -7805,16 +7786,16 @@
     </row>
     <row r="78" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="37" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C78" s="38" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D78" s="38" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E78" s="39"/>
       <c r="F78" s="39"/>
@@ -7824,19 +7805,19 @@
     </row>
     <row r="79" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="E79" s="22" t="s">
         <v>295</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>297</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="E79" s="22" t="s">
-        <v>299</v>
       </c>
       <c r="F79" s="41"/>
       <c r="G79" s="41"/>
@@ -7845,10 +7826,10 @@
     </row>
     <row r="80" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="37" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C80" s="39"/>
       <c r="D80" s="39"/>
@@ -7860,16 +7841,16 @@
     </row>
     <row r="81" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="40" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E81" s="41"/>
       <c r="F81" s="41"/>
@@ -7879,19 +7860,19 @@
     </row>
     <row r="82" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C82" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="D82" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E82" s="38" t="s">
         <v>305</v>
-      </c>
-      <c r="B82" s="38" t="s">
-        <v>306</v>
-      </c>
-      <c r="C82" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="D82" s="38" t="s">
-        <v>308</v>
-      </c>
-      <c r="E82" s="38" t="s">
-        <v>309</v>
       </c>
       <c r="F82" s="39"/>
       <c r="G82" s="39"/>
@@ -7900,10 +7881,10 @@
     </row>
     <row r="83" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="40" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C83" s="41"/>
       <c r="D83" s="41"/>
@@ -7915,16 +7896,16 @@
     </row>
     <row r="84" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="37" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C84" s="38" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D84" s="38" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E84" s="39"/>
       <c r="F84" s="39"/>
@@ -7934,22 +7915,22 @@
     </row>
     <row r="85" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="D85" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="B85" s="22" t="s">
+      <c r="F85" s="22" t="s">
         <v>317</v>
-      </c>
-      <c r="C85" s="22" t="s">
-        <v>318</v>
-      </c>
-      <c r="D85" s="22" t="s">
-        <v>319</v>
-      </c>
-      <c r="E85" s="22" t="s">
-        <v>320</v>
-      </c>
-      <c r="F85" s="22" t="s">
-        <v>321</v>
       </c>
       <c r="G85" s="41"/>
       <c r="H85" s="41"/>
@@ -7957,16 +7938,16 @@
     </row>
     <row r="86" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="37" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>323</v>
-      </c>
-      <c r="C86" s="38" t="s">
-        <v>324</v>
+        <v>319</v>
+      </c>
+      <c r="C86" s="42" t="s">
+        <v>1047</v>
       </c>
       <c r="D86" s="38" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E86" s="39"/>
       <c r="F86" s="39"/>
@@ -7976,18 +7957,20 @@
     </row>
     <row r="87" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="40" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C87" s="22" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D87" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E87" s="41"/>
+        <v>324</v>
+      </c>
+      <c r="E87" s="41" t="s">
+        <v>280</v>
+      </c>
       <c r="F87" s="41"/>
       <c r="G87" s="41"/>
       <c r="H87" s="41"/>
@@ -7995,16 +7978,16 @@
     </row>
     <row r="88" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="37" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B88" s="38" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C88" s="38" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D88" s="38" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E88" s="39"/>
       <c r="F88" s="39"/>
@@ -8014,19 +7997,19 @@
     </row>
     <row r="89" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="40" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C89" s="22" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E89" s="22" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="F89" s="41"/>
       <c r="G89" s="41"/>
@@ -8035,13 +8018,13 @@
     </row>
     <row r="90" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="37" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C90" s="38" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D90" s="39"/>
       <c r="E90" s="39"/>
@@ -8052,19 +8035,19 @@
     </row>
     <row r="91" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="40" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C91" s="22" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="E91" s="22" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="F91" s="41"/>
       <c r="G91" s="41"/>
@@ -8073,7 +8056,7 @@
     </row>
     <row r="92" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="37" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B92" s="39"/>
       <c r="C92" s="39"/>
@@ -8086,10 +8069,10 @@
     </row>
     <row r="93" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="40" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C93" s="41"/>
       <c r="D93" s="41"/>
@@ -8101,10 +8084,10 @@
     </row>
     <row r="94" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="37" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B94" s="38" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C94" s="39"/>
       <c r="D94" s="39"/>
@@ -8116,19 +8099,19 @@
     </row>
     <row r="95" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="40" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C95" s="22" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E95" s="22" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="F95" s="41"/>
       <c r="G95" s="41"/>
@@ -8137,19 +8120,19 @@
     </row>
     <row r="96" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="37" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B96" s="38" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C96" s="38" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D96" s="38" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E96" s="38" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F96" s="39"/>
       <c r="G96" s="39"/>
@@ -8158,10 +8141,10 @@
     </row>
     <row r="97" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="40" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C97" s="41"/>
       <c r="D97" s="41"/>
@@ -8173,19 +8156,19 @@
     </row>
     <row r="98" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="37" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B98" s="38" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C98" s="38" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D98" s="38" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E98" s="38" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F98" s="39"/>
       <c r="G98" s="39"/>
@@ -8194,13 +8177,13 @@
     </row>
     <row r="99" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="40" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D99" s="41"/>
       <c r="E99" s="41"/>
@@ -8211,19 +8194,19 @@
     </row>
     <row r="100" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="37" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B100" s="38" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C100" s="38" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E100" s="38" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="F100" s="39"/>
       <c r="G100" s="39"/>
@@ -8232,16 +8215,16 @@
     </row>
     <row r="101" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="40" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E101" s="41"/>
       <c r="F101" s="41"/>
@@ -8251,17 +8234,15 @@
     </row>
     <row r="102" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="37" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B102" s="38" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C102" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="D102" s="38" t="s">
-        <v>383</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="D102" s="38"/>
       <c r="E102" s="39"/>
       <c r="F102" s="39"/>
       <c r="G102" s="39"/>
@@ -8270,17 +8251,11 @@
     </row>
     <row r="103" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="40" t="s">
-        <v>384</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>385</v>
-      </c>
-      <c r="C103" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>387</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
       <c r="E103" s="41"/>
       <c r="F103" s="41"/>
       <c r="G103" s="41"/>
@@ -8289,16 +8264,16 @@
     </row>
     <row r="104" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="37" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B104" s="38" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C104" s="38" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D104" s="38" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E104" s="39"/>
       <c r="F104" s="39"/>
@@ -8308,7 +8283,7 @@
     </row>
     <row r="105" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="40" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B105" s="41"/>
       <c r="C105" s="41"/>
@@ -8321,10 +8296,10 @@
     </row>
     <row r="106" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="37" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B106" s="38" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C106" s="38" t="s">
         <v>157</v>
@@ -8338,33 +8313,37 @@
     </row>
     <row r="107" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="40" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C107" s="22" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E107" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="F107" s="41"/>
+        <v>389</v>
+      </c>
+      <c r="F107" s="41" t="s">
+        <v>221</v>
+      </c>
       <c r="G107" s="41"/>
       <c r="H107" s="41"/>
       <c r="I107" s="41"/>
     </row>
     <row r="108" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="37" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B108" s="38" t="s">
-        <v>399</v>
-      </c>
-      <c r="C108" s="39"/>
+        <v>390</v>
+      </c>
+      <c r="C108" s="39" t="s">
+        <v>221</v>
+      </c>
       <c r="D108" s="39"/>
       <c r="E108" s="39"/>
       <c r="F108" s="39"/>
@@ -8374,19 +8353,19 @@
     </row>
     <row r="109" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="40" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C109" s="22" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F109" s="41"/>
       <c r="G109" s="41"/>
@@ -8395,17 +8374,13 @@
     </row>
     <row r="110" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="37" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B110" s="38" t="s">
-        <v>406</v>
-      </c>
-      <c r="C110" s="38" t="s">
-        <v>407</v>
-      </c>
-      <c r="D110" s="38" t="s">
-        <v>408</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="C110" s="38"/>
+      <c r="D110" s="39"/>
       <c r="E110" s="39"/>
       <c r="F110" s="39"/>
       <c r="G110" s="39"/>
@@ -8414,10 +8389,10 @@
     </row>
     <row r="111" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="40" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C111" s="41"/>
       <c r="D111" s="41"/>
@@ -8429,13 +8404,13 @@
     </row>
     <row r="112" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="37" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="B112" s="38" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C112" s="38" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D112" s="39"/>
       <c r="E112" s="39"/>
@@ -8446,16 +8421,16 @@
     </row>
     <row r="113" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="40" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C113" s="22" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="D113" s="22" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E113" s="41"/>
       <c r="F113" s="41"/>
@@ -8465,16 +8440,16 @@
     </row>
     <row r="114" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="37" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B114" s="38" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="C114" s="38" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="D114" s="38" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="E114" s="39"/>
       <c r="F114" s="39"/>
@@ -8484,13 +8459,13 @@
     </row>
     <row r="115" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="40" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="C115" s="22" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="D115" s="41"/>
       <c r="E115" s="41"/>
@@ -8501,19 +8476,19 @@
     </row>
     <row r="116" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="37" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="B116" s="38" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C116" s="38" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D116" s="38" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="E116" s="38" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="F116" s="39"/>
       <c r="G116" s="39"/>
@@ -8522,19 +8497,19 @@
     </row>
     <row r="117" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="40" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C117" s="22" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D117" s="22" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="E117" s="22" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="F117" s="41"/>
       <c r="G117" s="41"/>
@@ -8543,16 +8518,16 @@
     </row>
     <row r="118" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="37" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B118" s="38" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="C118" s="38" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D118" s="38" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E118" s="39"/>
       <c r="F118" s="39"/>
@@ -8562,10 +8537,10 @@
     </row>
     <row r="119" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="40" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="C119" s="41"/>
       <c r="D119" s="41"/>
@@ -8577,19 +8552,19 @@
     </row>
     <row r="120" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="37" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B120" s="38" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C120" s="38" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="D120" s="38" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E120" s="38" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="F120" s="39"/>
       <c r="G120" s="39"/>
@@ -8598,16 +8573,16 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="40" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B121" s="22" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C121" s="22" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E121" s="41"/>
       <c r="F121" s="41"/>
@@ -8617,43 +8592,43 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="37" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="B122" s="38" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C122" s="38" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D122" s="38" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E122" s="38" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F122" s="38" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G122" s="38" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="H122" s="38" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="I122" s="39"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="40" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C123" s="22" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="D123" s="22" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="E123" s="41"/>
       <c r="F123" s="41"/>
@@ -8663,16 +8638,16 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="37" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="B124" s="38" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C124" s="38" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="D124" s="38" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="E124" s="39"/>
       <c r="F124" s="39"/>
@@ -8682,22 +8657,22 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="40" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="C125" s="22" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="E125" s="22" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="G125" s="41"/>
       <c r="H125" s="41"/>
@@ -8705,13 +8680,13 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="37" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="B126" s="38" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C126" s="38" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D126" s="39"/>
       <c r="E126" s="39"/>
@@ -8722,16 +8697,16 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="40" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="C127" s="22" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E127" s="41"/>
       <c r="F127" s="41"/>
@@ -8741,16 +8716,16 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="37" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B128" s="38" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C128" s="38" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="D128" s="38" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="E128" s="39"/>
       <c r="F128" s="39"/>
@@ -8760,13 +8735,13 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="40" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D129" s="41"/>
       <c r="E129" s="41"/>
@@ -8777,19 +8752,19 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="37" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B130" s="38" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="C130" s="38" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="D130" s="38" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="E130" s="38" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="F130" s="39"/>
       <c r="G130" s="39"/>
@@ -8798,13 +8773,13 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="40" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="C131" s="22" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="D131" s="41"/>
       <c r="E131" s="41"/>
@@ -8815,16 +8790,16 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="37" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B132" s="38" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C132" s="38" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D132" s="38" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="E132" s="39"/>
       <c r="F132" s="39"/>
@@ -8834,16 +8809,16 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="40" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="C133" s="22" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="D133" s="22" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="E133" s="41"/>
       <c r="F133" s="41"/>
@@ -8853,16 +8828,16 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="37" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="B134" s="38" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="C134" s="38" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="D134" s="38" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="E134" s="39"/>
       <c r="F134" s="39"/>
@@ -8872,10 +8847,10 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="40" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="C135" s="41"/>
       <c r="D135" s="41"/>
@@ -8887,10 +8862,10 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="37" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="B136" s="38" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C136" s="39"/>
       <c r="D136" s="39"/>
@@ -8902,16 +8877,16 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="40" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="C137" s="22" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="D137" s="22" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="E137" s="41"/>
       <c r="F137" s="41"/>
@@ -8921,13 +8896,13 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="37" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B138" s="38" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="C138" s="38" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="D138" s="39"/>
       <c r="E138" s="39"/>
@@ -8938,13 +8913,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="40" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="C139" s="22" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="D139" s="41"/>
       <c r="E139" s="41"/>
@@ -8955,10 +8930,10 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="37" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B140" s="38" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="C140" s="39"/>
       <c r="D140" s="39"/>
@@ -8970,10 +8945,10 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="40" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="C141" s="41"/>
       <c r="D141" s="41"/>
@@ -8985,16 +8960,16 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="37" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="B142" s="38" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="C142" s="38" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="D142" s="38" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="E142" s="39"/>
       <c r="F142" s="39"/>
@@ -9004,10 +8979,10 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="40" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="C143" s="41"/>
       <c r="D143" s="41"/>
@@ -9019,13 +8994,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="37" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="B144" s="38" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="C144" s="38" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="D144" s="39"/>
       <c r="E144" s="39"/>
@@ -9036,16 +9011,16 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="40" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="C145" s="22" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="D145" s="22" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="E145" s="41"/>
       <c r="F145" s="41"/>
@@ -9055,16 +9030,16 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="37" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="B146" s="38" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="C146" s="38" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="D146" s="38" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="E146" s="39"/>
       <c r="F146" s="39"/>
@@ -9074,13 +9049,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="40" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="C147" s="22" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D147" s="41"/>
       <c r="E147" s="41"/>
@@ -9091,46 +9066,46 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="37" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="B148" s="38" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="C148" s="38" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="D148" s="38" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="E148" s="38" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="F148" s="38" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="G148" s="38" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="H148" s="38" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="I148" s="39"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="40" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="C149" s="22" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="D149" s="22" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="E149" s="22" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="F149" s="41"/>
       <c r="G149" s="41"/>
@@ -9139,16 +9114,16 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="37" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="B150" s="38" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="C150" s="38" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="D150" s="38" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="E150" s="39"/>
       <c r="F150" s="39"/>
@@ -9158,10 +9133,10 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="40" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C151" s="41"/>
       <c r="D151" s="41"/>
@@ -9173,10 +9148,10 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="37" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="B152" s="38" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="C152" s="39"/>
       <c r="D152" s="39"/>
@@ -9188,16 +9163,16 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="40" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B153" s="22" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="D153" s="22" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="E153" s="41"/>
       <c r="F153" s="41"/>
@@ -9207,16 +9182,16 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="37" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="B154" s="38" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C154" s="38" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="D154" s="38" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="E154" s="39"/>
       <c r="F154" s="39"/>
@@ -9226,16 +9201,16 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="40" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B155" s="22" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D155" s="22" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="E155" s="41"/>
       <c r="F155" s="41"/>
@@ -9245,19 +9220,19 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="37" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="B156" s="38" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C156" s="38" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="D156" s="38" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="E156" s="38" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="F156" s="39"/>
       <c r="G156" s="39"/>
@@ -9266,13 +9241,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="40" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="D157" s="41"/>
       <c r="E157" s="41"/>
@@ -9283,16 +9258,16 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="37" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B158" s="38" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C158" s="38" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D158" s="38" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="E158" s="39"/>
       <c r="F158" s="39"/>
@@ -9302,10 +9277,10 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="40" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C159" s="41"/>
       <c r="D159" s="41"/>
@@ -9317,16 +9292,16 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="37" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="B160" s="38" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C160" s="38" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="D160" s="38" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="E160" s="39"/>
       <c r="F160" s="39"/>
@@ -9336,16 +9311,16 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="40" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D161" s="22" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="E161" s="41"/>
       <c r="F161" s="41"/>
@@ -9355,19 +9330,19 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="37" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B162" s="38" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C162" s="38" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="D162" s="38" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="E162" s="38" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="F162" s="39"/>
       <c r="G162" s="39"/>
@@ -9376,13 +9351,13 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="40" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="D163" s="41"/>
       <c r="E163" s="41"/>
@@ -9393,19 +9368,19 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="37" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="B164" s="38" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C164" s="38" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D164" s="38" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="E164" s="38" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="F164" s="39"/>
       <c r="G164" s="39"/>
@@ -9414,19 +9389,19 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="40" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="E165" s="22" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="F165" s="41"/>
       <c r="G165" s="41"/>
@@ -9435,19 +9410,19 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="37" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="B166" s="38" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="C166" s="38" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="D166" s="38" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="E166" s="38" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="F166" s="39"/>
       <c r="G166" s="39"/>
@@ -9456,19 +9431,19 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="40" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="C167" s="22" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="E167" s="22" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="F167" s="41"/>
       <c r="G167" s="41"/>
@@ -9477,16 +9452,16 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="37" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="B168" s="38" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="C168" s="38" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="D168" s="38" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="E168" s="39"/>
       <c r="F168" s="39"/>
@@ -9496,16 +9471,16 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="40" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C169" s="22" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="E169" s="41"/>
       <c r="F169" s="41"/>
@@ -9515,16 +9490,16 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="37" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="B170" s="38" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="C170" s="38" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="D170" s="38" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="E170" s="39"/>
       <c r="F170" s="39"/>
@@ -9534,16 +9509,16 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="40" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="E171" s="41"/>
       <c r="F171" s="41"/>
@@ -9553,10 +9528,10 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="37" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="B172" s="38" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="C172" s="39"/>
       <c r="D172" s="39"/>
@@ -9568,13 +9543,13 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="40" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="C173" s="22" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="D173" s="41"/>
       <c r="E173" s="41"/>
@@ -9585,16 +9560,16 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="37" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="B174" s="38" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="C174" s="38" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="D174" s="38" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="E174" s="39"/>
       <c r="F174" s="39"/>
@@ -9604,16 +9579,16 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="40" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="C175" s="22" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="E175" s="41"/>
       <c r="F175" s="41"/>
@@ -9623,13 +9598,13 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="37" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="B176" s="38" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="C176" s="38" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="D176" s="39"/>
       <c r="E176" s="39"/>
@@ -9640,16 +9615,16 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="40" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C177" s="22" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="D177" s="22" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="E177" s="41"/>
       <c r="F177" s="41"/>
@@ -9659,13 +9634,13 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="37" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="B178" s="38" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="C178" s="38" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="D178" s="39"/>
       <c r="E178" s="39"/>
@@ -9676,19 +9651,19 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="40" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="C179" s="22" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="D179" s="22" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="E179" s="22" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="F179" s="41"/>
       <c r="G179" s="41"/>
@@ -9697,16 +9672,16 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="37" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="B180" s="38" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="C180" s="38" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="D180" s="38" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="E180" s="39"/>
       <c r="F180" s="39"/>
@@ -9716,16 +9691,16 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="40" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="C181" s="22" t="s">
         <v>189</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="E181" s="41"/>
       <c r="F181" s="41"/>
@@ -9735,16 +9710,16 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="37" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="B182" s="38" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="C182" s="38" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="D182" s="38" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="E182" s="39"/>
       <c r="F182" s="39"/>
@@ -9754,22 +9729,22 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="40" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="C183" s="22" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="D183" s="22" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E183" s="22" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="F183" s="22" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="G183" s="41"/>
       <c r="H183" s="41"/>
@@ -9777,19 +9752,19 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="37" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="B184" s="38" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
       <c r="C184" s="38" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="D184" s="38" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="E184" s="38" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="F184" s="39"/>
       <c r="G184" s="39"/>
@@ -9798,13 +9773,13 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="40" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="C185" s="22" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="D185" s="41"/>
       <c r="E185" s="41"/>
@@ -9815,10 +9790,10 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="37" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="B186" s="38" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="C186" s="39"/>
       <c r="D186" s="39"/>
@@ -9830,19 +9805,19 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="40" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="C187" s="22" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
       <c r="E187" s="22" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="F187" s="41"/>
       <c r="G187" s="41"/>
@@ -9851,43 +9826,43 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="37" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="B188" s="38" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
       <c r="C188" s="38" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="D188" s="38" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E188" s="38" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="F188" s="38" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="G188" s="38" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="H188" s="38" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="I188" s="39"/>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="40" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="C189" s="22" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E189" s="41"/>
       <c r="F189" s="41"/>
@@ -9897,19 +9872,19 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="37" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="B190" s="38" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="C190" s="38" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="D190" s="38" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="E190" s="38" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="F190" s="39"/>
       <c r="G190" s="39"/>
@@ -9918,16 +9893,16 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="40" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="C191" s="22" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
       <c r="E191" s="41"/>
       <c r="F191" s="41"/>
@@ -9937,16 +9912,16 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="37" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="B192" s="38" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="C192" s="38" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="D192" s="38" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="E192" s="39"/>
       <c r="F192" s="39"/>
@@ -9956,16 +9931,16 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="40" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="C193" s="22" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="D193" s="22" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="E193" s="41"/>
       <c r="F193" s="41"/>
@@ -9975,16 +9950,16 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="37" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="B194" s="38" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="C194" s="38" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="D194" s="38" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="E194" s="39"/>
       <c r="F194" s="39"/>
@@ -9994,16 +9969,16 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="40" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C195" s="22" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="D195" s="22" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="E195" s="41"/>
       <c r="F195" s="41"/>
@@ -10013,16 +9988,16 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="37" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="B196" s="38" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="C196" s="38" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="D196" s="38" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="E196" s="39"/>
       <c r="F196" s="39"/>
@@ -10032,13 +10007,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="40" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="C197" s="22" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="D197" s="41"/>
       <c r="E197" s="41"/>
@@ -10049,16 +10024,16 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="37" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="B198" s="38" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="C198" s="38" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D198" s="38" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E198" s="39"/>
       <c r="F198" s="39"/>
@@ -10068,16 +10043,16 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="40" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="D199" s="22" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="E199" s="41"/>
       <c r="F199" s="41"/>
@@ -10087,13 +10062,13 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="37" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="B200" s="38" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="C200" s="38" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D200" s="39"/>
       <c r="E200" s="39"/>
@@ -10104,16 +10079,16 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="40" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D201" s="22" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E201" s="41"/>
       <c r="F201" s="41"/>
@@ -10123,19 +10098,19 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="37" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B202" s="38" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="C202" s="38" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="D202" s="38" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="E202" s="38" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="F202" s="39"/>
       <c r="G202" s="39"/>
@@ -10144,19 +10119,19 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="40" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="D203" s="22" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="E203" s="22" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="F203" s="41"/>
       <c r="G203" s="41"/>
@@ -10165,13 +10140,13 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="37" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B204" s="38" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="C204" s="38" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="D204" s="39"/>
       <c r="E204" s="39"/>
@@ -10182,16 +10157,16 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="40" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="E205" s="41"/>
       <c r="F205" s="41"/>
@@ -10201,10 +10176,10 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="37" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="B206" s="38" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="C206" s="39"/>
       <c r="D206" s="39"/>
@@ -10216,13 +10191,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="40" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
       <c r="D207" s="41"/>
       <c r="E207" s="41"/>
@@ -10233,13 +10208,13 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="37" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="B208" s="38" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="C208" s="38" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="D208" s="39"/>
       <c r="E208" s="39"/>
@@ -10250,19 +10225,19 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="40" t="s">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C209" s="22" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="E209" s="22" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="F209" s="41"/>
       <c r="G209" s="41"/>
@@ -10271,10 +10246,10 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="37" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="B210" s="38" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="C210" s="39"/>
       <c r="D210" s="39"/>
@@ -10286,16 +10261,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="40" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="C211" s="22" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="E211" s="41"/>
       <c r="F211" s="41"/>
@@ -10305,16 +10280,16 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="37" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="B212" s="38" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
       <c r="C212" s="38" t="s">
-        <v>778</v>
+        <v>767</v>
       </c>
       <c r="D212" s="38" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="E212" s="39"/>
       <c r="F212" s="39"/>
@@ -10324,10 +10299,10 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="40" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="C213" s="22" t="s">
         <v>155</v>
@@ -10341,16 +10316,16 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="37" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B214" s="38" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="C214" s="38" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="D214" s="38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E214" s="39"/>
       <c r="F214" s="39"/>
@@ -10360,13 +10335,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="40" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
       <c r="B215" s="22" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="C215" s="22" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
       <c r="D215" s="41"/>
       <c r="E215" s="41"/>
@@ -10377,16 +10352,16 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="37" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="B216" s="38" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="C216" s="38" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="D216" s="38" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
       <c r="E216" s="39"/>
       <c r="F216" s="39"/>
@@ -10396,19 +10371,19 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="40" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="B217" s="22" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="C217" s="22" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="E217" s="22" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="F217" s="41"/>
       <c r="G217" s="41"/>
@@ -10417,13 +10392,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="37" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="B218" s="38" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="C218" s="38" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="D218" s="39"/>
       <c r="E218" s="39"/>
@@ -10434,19 +10409,19 @@
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="40" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="B219" s="22" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="C219" s="22" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="E219" s="22" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="F219" s="41"/>
       <c r="G219" s="41"/>
@@ -10455,13 +10430,13 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="37" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="B220" s="38" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="C220" s="38" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="D220" s="39"/>
       <c r="E220" s="39"/>
@@ -10472,16 +10447,16 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="40" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="B221" s="22" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="C221" s="22" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="E221" s="41"/>
       <c r="F221" s="41"/>
@@ -10491,16 +10466,16 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="37" t="s">
-        <v>808</v>
+        <v>797</v>
       </c>
       <c r="B222" s="38" t="s">
-        <v>809</v>
+        <v>798</v>
       </c>
       <c r="C222" s="38" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
       <c r="D222" s="38" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="E222" s="39"/>
       <c r="F222" s="39"/>
@@ -10510,19 +10485,19 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="40" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="B223" s="22" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="C223" s="22" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="E223" s="22" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="F223" s="41"/>
       <c r="G223" s="41"/>
@@ -10531,13 +10506,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="37" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="B224" s="38" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="C224" s="38" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="D224" s="39"/>
       <c r="E224" s="39"/>
@@ -10548,10 +10523,10 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="40" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="B225" s="22" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="C225" s="41"/>
       <c r="D225" s="41"/>
@@ -10563,16 +10538,16 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="37" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="B226" s="38" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
       <c r="C226" s="38" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="D226" s="38" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="E226" s="39"/>
       <c r="F226" s="39"/>
@@ -10582,16 +10557,16 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="40" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="B227" s="22" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="C227" s="22" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
       <c r="E227" s="41"/>
       <c r="F227" s="41"/>
@@ -10601,16 +10576,16 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="37" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
       <c r="B228" s="38" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="C228" s="38" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="D228" s="38" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="E228" s="39"/>
       <c r="F228" s="39"/>
@@ -10620,13 +10595,13 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="40" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="B229" s="22" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="C229" s="22" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="D229" s="41"/>
       <c r="E229" s="41"/>
@@ -10637,19 +10612,19 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="37" t="s">
-        <v>834</v>
+        <v>823</v>
       </c>
       <c r="B230" s="38" t="s">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="C230" s="38" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="D230" s="38" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="E230" s="38" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="F230" s="39"/>
       <c r="G230" s="39"/>
@@ -10658,13 +10633,13 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="40" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="B231" s="22" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="C231" s="22" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="D231" s="41"/>
       <c r="E231" s="41"/>
@@ -10675,13 +10650,13 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="37" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="B232" s="38" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="C232" s="38" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="D232" s="39"/>
       <c r="E232" s="39"/>
@@ -10692,19 +10667,19 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="40" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="B233" s="22" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="C233" s="22" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
       <c r="E233" s="22" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
       <c r="F233" s="41"/>
       <c r="G233" s="41"/>
@@ -10713,19 +10688,19 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="37" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
       <c r="B234" s="38" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
       <c r="C234" s="38" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="D234" s="38" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
       <c r="E234" s="38" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
       <c r="F234" s="39"/>
       <c r="G234" s="39"/>
@@ -10734,16 +10709,16 @@
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="40" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="B235" s="22" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="C235" s="22" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
       <c r="E235" s="41"/>
       <c r="F235" s="41"/>
@@ -10753,19 +10728,19 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="37" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="B236" s="38" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="C236" s="38" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="D236" s="38" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
       <c r="E236" s="38" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="F236" s="39"/>
       <c r="G236" s="39"/>
@@ -10774,13 +10749,13 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="40" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="B237" s="22" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
       <c r="C237" s="22" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
       <c r="D237" s="41"/>
       <c r="E237" s="41"/>
@@ -10791,13 +10766,13 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="37" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="B238" s="38" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="C238" s="38" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="D238" s="39"/>
       <c r="E238" s="39"/>
@@ -10808,16 +10783,16 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="40" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
       <c r="B239" s="22" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="C239" s="22" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>873</v>
+        <v>862</v>
       </c>
       <c r="E239" s="41"/>
       <c r="F239" s="41"/>
@@ -10827,16 +10802,16 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="37" t="s">
-        <v>874</v>
+        <v>863</v>
       </c>
       <c r="B240" s="38" t="s">
-        <v>875</v>
+        <v>864</v>
       </c>
       <c r="C240" s="38" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="D240" s="38" t="s">
-        <v>876</v>
+        <v>865</v>
       </c>
       <c r="E240" s="39"/>
       <c r="F240" s="39"/>
@@ -10846,16 +10821,16 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="40" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="B241" s="22" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="C241" s="22" t="s">
-        <v>879</v>
+        <v>868</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="E241" s="41"/>
       <c r="F241" s="41"/>
@@ -10865,13 +10840,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="37" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="B242" s="38" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="C242" s="38" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="D242" s="39"/>
       <c r="E242" s="39"/>
@@ -10882,16 +10857,16 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="40" t="s">
-        <v>884</v>
+        <v>873</v>
       </c>
       <c r="B243" s="22" t="s">
-        <v>885</v>
+        <v>874</v>
       </c>
       <c r="C243" s="22" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="E243" s="41"/>
       <c r="F243" s="41"/>
@@ -10901,10 +10876,10 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="37" t="s">
-        <v>888</v>
+        <v>877</v>
       </c>
       <c r="B244" s="38" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="C244" s="39"/>
       <c r="D244" s="39"/>
@@ -10916,16 +10891,16 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="40" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="B245" s="22" t="s">
-        <v>891</v>
+        <v>880</v>
       </c>
       <c r="C245" s="22" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="E245" s="41"/>
       <c r="F245" s="41"/>
@@ -10935,16 +10910,16 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="37" t="s">
-        <v>894</v>
+        <v>883</v>
       </c>
       <c r="B246" s="38" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="C246" s="38" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="D246" s="38" t="s">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="E246" s="39"/>
       <c r="F246" s="39"/>
@@ -10954,13 +10929,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="40" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="B247" s="22" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="C247" s="22" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="D247" s="41"/>
       <c r="E247" s="41"/>
@@ -10971,13 +10946,13 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="37" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="B248" s="38" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="C248" s="38" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="D248" s="38" t="s">
         <v>130</v>
@@ -10990,10 +10965,10 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="40" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="B249" s="22" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="C249" s="41"/>
       <c r="D249" s="41"/>
@@ -11005,13 +10980,13 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="37" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="B250" s="38" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="C250" s="38" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="D250" s="39"/>
       <c r="E250" s="39"/>
@@ -11022,16 +10997,16 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="40" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
       <c r="B251" s="22" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="C251" s="22" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="E251" s="41"/>
       <c r="F251" s="41"/>
@@ -11041,16 +11016,16 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="37" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B252" s="38" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="C252" s="38" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="D252" s="38" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="E252" s="39"/>
       <c r="F252" s="39"/>
@@ -11060,13 +11035,13 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="40" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>915</v>
+        <v>904</v>
       </c>
       <c r="C253" s="22" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="D253" s="41"/>
       <c r="E253" s="41"/>
@@ -11077,10 +11052,10 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="37" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="B254" s="38" t="s">
-        <v>918</v>
+        <v>907</v>
       </c>
       <c r="C254" s="39"/>
       <c r="D254" s="39"/>
@@ -11092,16 +11067,16 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="40" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="B255" s="22" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
       <c r="C255" s="22" t="s">
-        <v>921</v>
+        <v>910</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>922</v>
+        <v>911</v>
       </c>
       <c r="E255" s="41"/>
       <c r="F255" s="41"/>
@@ -11111,10 +11086,10 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="37" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
       <c r="B256" s="38" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C256" s="39"/>
       <c r="D256" s="39"/>
@@ -11126,16 +11101,16 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="40" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
       <c r="B257" s="22" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="C257" s="22" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="E257" s="41"/>
       <c r="F257" s="41"/>
@@ -11145,10 +11120,10 @@
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="37" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B258" s="38" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="C258" s="38" t="s">
         <v>157</v>
@@ -11162,13 +11137,13 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="40" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="B259" s="22" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="C259" s="22" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="D259" s="41"/>
       <c r="E259" s="41"/>
@@ -11179,16 +11154,16 @@
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="37" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="B260" s="38" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="C260" s="38" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="D260" s="38" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="E260" s="39"/>
       <c r="F260" s="39"/>
@@ -11198,16 +11173,16 @@
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="40" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="B261" s="22" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="C261" s="22" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="E261" s="41"/>
       <c r="F261" s="41"/>
@@ -11217,19 +11192,19 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="37" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="B262" s="38" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="C262" s="38" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="D262" s="38" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="E262" s="38" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="F262" s="39"/>
       <c r="G262" s="39"/>
@@ -11238,10 +11213,10 @@
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="40" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="B263" s="22" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="C263" s="41"/>
       <c r="D263" s="41"/>
@@ -11253,16 +11228,16 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="37" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="B264" s="38" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="C264" s="38" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="D264" s="38" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="E264" s="39"/>
       <c r="F264" s="39"/>
@@ -11272,16 +11247,16 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="40" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="B265" s="22" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="C265" s="22" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="E265" s="41"/>
       <c r="F265" s="41"/>
@@ -11291,16 +11266,16 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="37" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="B266" s="38" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="C266" s="38" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="D266" s="38" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="E266" s="39"/>
       <c r="F266" s="39"/>
@@ -11310,16 +11285,16 @@
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="40" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B267" s="22" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="C267" s="22" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="E267" s="41"/>
       <c r="F267" s="41"/>
@@ -11329,16 +11304,16 @@
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="37" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="B268" s="38" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="C268" s="38" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="D268" s="38" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="E268" s="39"/>
       <c r="F268" s="39"/>
@@ -11348,13 +11323,13 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="40" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B269" s="22" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="C269" s="22" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="D269" s="41"/>
       <c r="E269" s="41"/>
@@ -11365,13 +11340,13 @@
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="37" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="B270" s="38" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="C270" s="38" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="D270" s="39"/>
       <c r="E270" s="39"/>
@@ -11382,16 +11357,16 @@
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="40" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B271" s="22" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="C271" s="22" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="E271" s="41"/>
       <c r="F271" s="41"/>
@@ -11401,19 +11376,19 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="37" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B272" s="38" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="C272" s="38" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="D272" s="38" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="E272" s="38" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="F272" s="39"/>
       <c r="G272" s="39"/>
@@ -11422,16 +11397,16 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="40" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="B273" s="22" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="C273" s="22" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="E273" s="41"/>
       <c r="F273" s="41"/>
@@ -11441,44 +11416,44 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="37" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B274" s="38" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="C274" s="38" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="D274" s="38" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="E274" s="38" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="F274" s="38" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="G274" s="38" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="H274" s="39"/>
       <c r="I274" s="39"/>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="40" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B275" s="22" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="C275" s="22" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="E275" s="22" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="F275" s="41"/>
       <c r="G275" s="41"/>
@@ -11487,13 +11462,13 @@
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="37" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="B276" s="38" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="C276" s="38" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="D276" s="39"/>
       <c r="E276" s="39"/>
@@ -11504,13 +11479,13 @@
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="40" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="B277" s="22" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="C277" s="22" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="D277" s="41"/>
       <c r="E277" s="41"/>
@@ -11521,10 +11496,10 @@
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="37" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="B278" s="38" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="C278" s="39"/>
       <c r="D278" s="39"/>
@@ -11536,16 +11511,16 @@
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="40" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="B279" s="22" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="C279" s="22" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="E279" s="41"/>
       <c r="F279" s="41"/>
@@ -11555,16 +11530,16 @@
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="37" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="B280" s="38" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="C280" s="38" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="D280" s="38" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="E280" s="39"/>
       <c r="F280" s="39"/>
@@ -11574,19 +11549,19 @@
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="40" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="B281" s="22" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="C281" s="22" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="E281" s="22" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="F281" s="41"/>
       <c r="G281" s="41"/>
@@ -11595,10 +11570,10 @@
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="37" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="B282" s="38" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="C282" s="39"/>
       <c r="D282" s="39"/>
@@ -11610,16 +11585,16 @@
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="40" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="B283" s="22" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="C283" s="22" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="E283" s="41"/>
       <c r="F283" s="41"/>
@@ -11629,13 +11604,13 @@
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="37" t="s">
-        <v>1011</v>
+        <v>1000</v>
       </c>
       <c r="B284" s="38" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="C284" s="38" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="D284" s="39"/>
       <c r="E284" s="39"/>
@@ -11646,22 +11621,22 @@
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="40" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
       <c r="B285" s="22" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="C285" s="22" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
       <c r="E285" s="22" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
       <c r="G285" s="41"/>
       <c r="H285" s="41"/>
@@ -11669,16 +11644,16 @@
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="37" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="B286" s="38" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="C286" s="38" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="D286" s="38" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
       <c r="E286" s="39"/>
       <c r="F286" s="39"/>
@@ -11688,13 +11663,13 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="40" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
       <c r="B287" s="22" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="C287" s="22" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="D287" s="41"/>
       <c r="E287" s="41"/>
@@ -11705,16 +11680,16 @@
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="37" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="B288" s="38" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="C288" s="38" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="D288" s="38" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="E288" s="39"/>
       <c r="F288" s="39"/>

--- a/public/images/items/ingredienten_categorieen.xlsx
+++ b/public/images/items/ingredienten_categorieen.xlsx
@@ -504,7 +504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B336"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3066,16 +3066,144 @@
         <v>Conserven, Sauzen, Olie &amp; Kruiden</v>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>chips_croky_paprika_rings</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Zoute Snacks</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>chips_paprika</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Zoute Snacks</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>chips_pickles</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Zoute Snacks</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>chips_salt_and_vinegar</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Zoute Snacks</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>chips_zout</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Zoute Snacks</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>confituur</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Beleg</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>coquilles</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Vis &amp; Zeevruchten</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>gerookte_zalmhaasje</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Vis &amp; Zeevruchten</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>huishoudfolie</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Huishouden &amp; Schoonmaak</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>pompoen</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Groenten &amp; Fruit</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>smeerboter</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Zuivel, Kaas &amp; Eieren</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>speculoospasta</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Beleg</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>vol-au-vent_koekje</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Diepvries</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>vol-au-vent_voorgemaakt</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Diepvries</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>zuur_fruit_snoep</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Snoep &amp; Chocolade</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>vleesje_noë</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Vlees &amp; Charcuterie</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B320"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B336"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I291"/>
+  <dimension ref="A1:I309"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3113,6 +3241,27 @@
       <c r="B2" t="str">
         <v>batterijen</v>
       </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -3156,6 +3305,21 @@
       <c r="D4" t="str">
         <v>patattenbollekes</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -3164,6 +3328,27 @@
       <c r="B5" t="str">
         <v>aardbei</v>
       </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3178,6 +3363,21 @@
       <c r="D6" t="str">
         <v>broodjes_om_te_bakken</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3192,6 +3392,21 @@
       <c r="D7" t="str">
         <v>ajuin</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -3209,13 +3424,46 @@
       <c r="E8" t="str">
         <v>schoonmaakmiddel</v>
       </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>alpro_kokosdrink</v>
       </c>
       <c r="B9" t="str">
+        <v>alpro kokosdrink</v>
+      </c>
+      <c r="C9" t="str">
         <v>kokosdrink</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3223,10 +3471,28 @@
         <v>alpro_vanilla_dessert</v>
       </c>
       <c r="B10" t="str">
-        <v>vanille_dessert</v>
+        <v>alpro vanilla dessert</v>
       </c>
       <c r="C10" t="str">
-        <v>pudding</v>
+        <v>vanille dessert</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3245,6 +3511,18 @@
       <c r="E11" t="str">
         <v>bittere_amandel</v>
       </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3259,6 +3537,21 @@
       <c r="D12" t="str">
         <v>fijngemalen_amandelen</v>
       </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3273,6 +3566,21 @@
       <c r="D13" t="str">
         <v>notenmelk</v>
       </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -3290,6 +3598,18 @@
       <c r="E14" t="str">
         <v>filet_americain</v>
       </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -3301,6 +3621,24 @@
       <c r="C15" t="str">
         <v>pink_lady</v>
       </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -3315,6 +3653,21 @@
       <c r="D16" t="str">
         <v>neutrale_olie</v>
       </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -3323,6 +3676,27 @@
       <c r="B17" t="str">
         <v>aubergines</v>
       </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -3334,6 +3708,24 @@
       <c r="C18" t="str">
         <v>cornichon</v>
       </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3342,16 +3734,55 @@
       <c r="B19" t="str">
         <v>boter</v>
       </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>baking_soda</v>
       </c>
       <c r="B20" t="str">
+        <v>baking soda</v>
+      </c>
+      <c r="C20" t="str">
         <v>zuiveringszout</v>
       </c>
-      <c r="C20" t="str">
-        <v>bicarbonaat</v>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3364,6 +3795,24 @@
       <c r="C21" t="str">
         <v>ovenfolie</v>
       </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -3381,6 +3830,18 @@
       <c r="E22" t="str">
         <v>levure_chimique</v>
       </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -3389,6 +3850,27 @@
       <c r="B23" t="str">
         <v>banaan</v>
       </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -3397,6 +3879,27 @@
       <c r="B24" t="str">
         <v>verse_basilicum</v>
       </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -3414,6 +3917,18 @@
       <c r="E25" t="str">
         <v>sauce_bechamel</v>
       </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -3428,6 +3943,21 @@
       <c r="D26" t="str">
         <v>bellenblazer</v>
       </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3436,6 +3966,27 @@
       <c r="B27" t="str">
         <v>verse_bieslook</v>
       </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -3447,6 +3998,24 @@
       <c r="C28" t="str">
         <v>bitterballen_diepvries</v>
       </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3461,6 +4030,21 @@
       <c r="D29" t="str">
         <v>pate_feuilletee</v>
       </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -3469,6 +4053,27 @@
       <c r="B30" t="str">
         <v>tomatenblokjes</v>
       </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -3480,6 +4085,24 @@
       <c r="C31" t="str">
         <v>hele_gepelde_tomaten</v>
       </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -3488,6 +4111,27 @@
       <c r="B32" t="str">
         <v>icing_sugar</v>
       </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -3502,6 +4146,21 @@
       <c r="D33" t="str">
         <v>gemengde_diepvriesgroenten</v>
       </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -3516,6 +4175,21 @@
       <c r="D34" t="str">
         <v>bosbes</v>
       </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -3527,6 +4201,24 @@
       <c r="C35" t="str">
         <v>bruine_champignons</v>
       </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -3547,6 +4239,15 @@
       <c r="F36" t="str">
         <v>rode_vruchtenthee</v>
       </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -3561,6 +4262,21 @@
       <c r="D37" t="str">
         <v>broccolistengel</v>
       </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -3572,6 +4288,24 @@
       <c r="C38" t="str">
         <v>donker_brood</v>
       </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -3586,6 +4320,21 @@
       <c r="D39" t="str">
         <v>boord_kristof</v>
       </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -3594,6 +4343,27 @@
       <c r="B40" t="str">
         <v>kinderbrood</v>
       </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -3611,6 +4381,18 @@
       <c r="E41" t="str">
         <v>rhum_brun</v>
       </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -3622,6 +4404,24 @@
       <c r="C42" t="str">
         <v>cassonade</v>
       </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -3630,13 +4430,55 @@
       <c r="B43" t="str">
         <v>pompoen</v>
       </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v>cacaopoeder</v>
       </c>
       <c r="B44" t="str">
-        <v>cacao_poeder</v>
+        <v>cacaopoeder</v>
+      </c>
+      <c r="C44" t="str">
+        <v>cacao poeder</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -3644,10 +4486,28 @@
         <v>cappellini_pasta</v>
       </c>
       <c r="B45" t="str">
+        <v>cappellini pasta</v>
+      </c>
+      <c r="C45" t="str">
         <v>cappellini</v>
       </c>
-      <c r="C45" t="str">
-        <v>spaghetti</v>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -3660,16 +4520,52 @@
       <c r="C46" t="str">
         <v>rauwe_rundvlees</v>
       </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v>carres_hele_hazelnoten_chocolade</v>
       </c>
       <c r="B47" t="str">
-        <v>carres_hazelnoot_chocolade</v>
+        <v>carres hele hazelnoten chocolade</v>
       </c>
       <c r="C47" t="str">
-        <v>hazelnoot_chocolade</v>
+        <v>carrés hazelnoot chocolade</v>
+      </c>
+      <c r="D47" t="str">
+        <v>hazelnoot chocolade</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3677,7 +4573,28 @@
         <v>cayennepeper</v>
       </c>
       <c r="B48" t="str">
-        <v>cayenne_peper</v>
+        <v>cayennepeper</v>
+      </c>
+      <c r="C48" t="str">
+        <v>cayenne peper</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3693,6 +4610,21 @@
       <c r="D49" t="str">
         <v>warme_chocomelk</v>
       </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3710,6 +4642,18 @@
       <c r="E50" t="str">
         <v>cava</v>
       </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -3721,6 +4665,24 @@
       <c r="C51" t="str">
         <v>paddenstoelen</v>
       </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3735,6 +4697,21 @@
       <c r="D52" t="str">
         <v>franse_kaas</v>
       </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3746,6 +4723,24 @@
       <c r="C53" t="str">
         <v>rode_peper</v>
       </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3760,6 +4755,21 @@
       <c r="D54" t="str">
         <v>kleine_worstjes</v>
       </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3774,6 +4784,21 @@
       <c r="D55" t="str">
         <v>zoute_chips</v>
       </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3782,6 +4807,27 @@
       <c r="B56" t="str">
         <v>pure_chocolade</v>
       </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3793,6 +4839,24 @@
       <c r="C57" t="str">
         <v>kindchocolade</v>
       </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3810,6 +4874,18 @@
       <c r="E58" t="str">
         <v>chocoladeschilfers</v>
       </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3821,6 +4897,24 @@
       <c r="C59" t="str">
         <v>chouffe_bier</v>
       </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3835,6 +4929,21 @@
       <c r="D60" t="str">
         <v>coke</v>
       </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -3849,6 +4958,21 @@
       <c r="D61" t="str">
         <v>apres_shampooing</v>
       </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3866,6 +4990,18 @@
       <c r="E62" t="str">
         <v>cornet_oaked</v>
       </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3877,13 +5013,52 @@
       <c r="C63" t="str">
         <v>groene_courgette</v>
       </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
         <v>curry_poeder</v>
       </c>
       <c r="B64" t="str">
+        <v>curry poeder</v>
+      </c>
+      <c r="C64" t="str">
         <v>kerriepoeder</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -3902,6 +5077,18 @@
       <c r="E65" t="str">
         <v>anti_transpirant</v>
       </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3913,6 +5100,24 @@
       <c r="C66" t="str">
         <v>afvoerreiniger</v>
       </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3930,6 +5135,18 @@
       <c r="E67" t="str">
         <v>handafwas</v>
       </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3938,6 +5155,27 @@
       <c r="B68" t="str">
         <v>droge_worst</v>
       </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3952,6 +5190,21 @@
       <c r="D69" t="str">
         <v>zwarte_thee</v>
       </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3966,6 +5219,21 @@
       <c r="D70" t="str">
         <v>groene_sojabonen</v>
       </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3983,6 +5251,18 @@
       <c r="E71" t="str">
         <v>doosje_eieren</v>
       </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3991,6 +5271,27 @@
       <c r="B72" t="str">
         <v>eieren</v>
       </c>
+      <c r="C72" t="str">
+        <v/>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4008,16 +5309,46 @@
       <c r="E73" t="str">
         <v>petits_pois</v>
       </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
         <v>ferrero_rocher_chocolade</v>
       </c>
       <c r="B74" t="str">
-        <v>ferrero_rocher</v>
+        <v>ferrero rocher chocolade</v>
       </c>
       <c r="C74" t="str">
+        <v>ferrero rocher</v>
+      </c>
+      <c r="D74" t="str">
         <v>rocher</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -4027,6 +5358,27 @@
       <c r="B75" t="str">
         <v>framboos</v>
       </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4041,6 +5393,21 @@
       <c r="D76" t="str">
         <v>yoghurtdrank</v>
       </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4058,6 +5425,18 @@
       <c r="E77" t="str">
         <v>patat</v>
       </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4072,6 +5451,21 @@
       <c r="D78" t="str">
         <v>bakvet</v>
       </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4086,6 +5480,21 @@
       <c r="D79" t="str">
         <v>saucisson_sec</v>
       </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4100,6 +5509,21 @@
       <c r="D80" t="str">
         <v>crevetten</v>
       </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4117,6 +5541,18 @@
       <c r="E81" t="str">
         <v>hele_kip</v>
       </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4134,6 +5570,18 @@
       <c r="E82" t="str">
         <v>gemengd_gehakt</v>
       </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4142,6 +5590,27 @@
       <c r="B83" t="str">
         <v>balletjes</v>
       </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4150,6 +5619,27 @@
       <c r="B84" t="str">
         <v>verse_gember</v>
       </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4158,6 +5648,27 @@
       <c r="B85" t="str">
         <v>thee</v>
       </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4172,6 +5683,21 @@
       <c r="D86" t="str">
         <v>gemalen_kaas</v>
       </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4186,13 +5712,49 @@
       <c r="D87" t="str">
         <v>tortelloni</v>
       </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
         <v>ginger_beer</v>
       </c>
       <c r="B88" t="str">
+        <v>ginger beer</v>
+      </c>
+      <c r="C88" t="str">
         <v>gemberbier</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -4211,6 +5773,18 @@
       <c r="E89" t="str">
         <v>vensterreiniger</v>
       </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4219,6 +5793,27 @@
       <c r="B90" t="str">
         <v>sportdrank</v>
       </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4230,6 +5825,24 @@
       <c r="C91" t="str">
         <v>mechels_bier</v>
       </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4241,6 +5854,24 @@
       <c r="C92" t="str">
         <v>volle_yoghurt</v>
       </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4258,6 +5889,18 @@
       <c r="E93" t="str">
         <v>pralines</v>
       </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4266,6 +5909,27 @@
       <c r="B94" t="str">
         <v>chocolade</v>
       </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4280,6 +5944,21 @@
       <c r="D95" t="str">
         <v>beenham</v>
       </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4288,13 +5967,55 @@
       <c r="B96" t="str">
         <v>burger</v>
       </c>
+      <c r="C96" t="str">
+        <v/>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
         <v>handzeep</v>
       </c>
       <c r="B97" t="str">
+        <v>handzeep</v>
+      </c>
+      <c r="C97" t="str">
         <v>zeep</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -4304,6 +6025,27 @@
       <c r="B98" t="str">
         <v>vloeibare_honing</v>
       </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4315,6 +6057,24 @@
       <c r="C99" t="str">
         <v>lipton_ice_tea</v>
       </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4329,6 +6089,21 @@
       <c r="D100" t="str">
         <v>salade</v>
       </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4340,6 +6115,24 @@
       <c r="C101" t="str">
         <v>peper</v>
       </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4357,13 +6150,46 @@
       <c r="E102" t="str">
         <v>blond_bier</v>
       </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
         <v>kaas_blok</v>
       </c>
       <c r="B103" t="str">
-        <v>blok_kaas</v>
+        <v>kaas blok</v>
+      </c>
+      <c r="C103" t="str">
+        <v>blok kaas</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -4371,10 +6197,28 @@
         <v>kaas_blokjes</v>
       </c>
       <c r="B104" t="str">
-        <v>gouda</v>
+        <v>kaas blokjes</v>
       </c>
       <c r="C104" t="str">
-        <v>jonge_kaas</v>
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -4382,7 +6226,28 @@
         <v>kaas_sneetjes</v>
       </c>
       <c r="B105" t="str">
-        <v>plakken_kaas</v>
+        <v>kaas sneetjes</v>
+      </c>
+      <c r="C105" t="str">
+        <v>plakken kaas</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -4401,6 +6266,18 @@
       <c r="E106" t="str">
         <v>visfilet</v>
       </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4412,6 +6289,24 @@
       <c r="C107" t="str">
         <v>vleesje_noë</v>
       </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -4420,6 +6315,27 @@
       <c r="B108" t="str">
         <v>kalkoen</v>
       </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v/>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -4434,6 +6350,21 @@
       <c r="D109" t="str">
         <v>cannelle</v>
       </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -4448,16 +6379,49 @@
       <c r="D110" t="str">
         <v>bosteels</v>
       </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
         <v>kattekorrels</v>
       </c>
       <c r="B111" t="str">
+        <v>kattekorrels</v>
+      </c>
+      <c r="C111" t="str">
         <v>kattenkorrels</v>
       </c>
-      <c r="C111" t="str">
+      <c r="D111" t="str">
         <v>kattenvoer</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -4465,7 +6429,28 @@
         <v>kauwgom</v>
       </c>
       <c r="B112" t="str">
-        <v>chewing_gum</v>
+        <v>kauwgom</v>
+      </c>
+      <c r="C112" t="str">
+        <v>chewing gum</v>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -4493,6 +6478,9 @@
       <c r="H113" t="str">
         <v>tomaten</v>
       </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -4507,6 +6495,21 @@
       <c r="D114" t="str">
         <v>sauce_tomate</v>
       </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -4521,13 +6524,49 @@
       <c r="D115" t="str">
         <v>keuken_rol</v>
       </c>
+      <c r="E115" t="str">
+        <v/>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
         <v>kinder_surprise</v>
       </c>
       <c r="B116" t="str">
-        <v>kinder_ei</v>
+        <v>kinder surprise</v>
+      </c>
+      <c r="C116" t="str">
+        <v>kinder ei</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -4535,7 +6574,28 @@
         <v>kip_curry</v>
       </c>
       <c r="B117" t="str">
+        <v>kip curry</v>
+      </c>
+      <c r="C117" t="str">
         <v>kipcurry</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -4557,6 +6617,15 @@
       <c r="F118" t="str">
         <v>kippendijenfilet</v>
       </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4568,6 +6637,24 @@
       <c r="C119" t="str">
         <v>kippenborst</v>
       </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -4582,6 +6669,21 @@
       <c r="D120" t="str">
         <v>kipgehaktballetjes</v>
       </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -4596,6 +6698,21 @@
       <c r="D121" t="str">
         <v>kipreepjes</v>
       </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -4604,6 +6721,27 @@
       <c r="B122" t="str">
         <v>kipkruiden</v>
       </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -4618,6 +6756,21 @@
       <c r="D123" t="str">
         <v>kip_wraps</v>
       </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4629,6 +6782,24 @@
       <c r="C124" t="str">
         <v>worsten</v>
       </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v/>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -4637,16 +6808,55 @@
       <c r="B125" t="str">
         <v>kippenschnitzel</v>
       </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
         <v>kleine_flesje_wijn_rood</v>
       </c>
       <c r="B126" t="str">
-        <v>kleine_fles_wijn_rood</v>
+        <v>kleine flesje wijn rood</v>
       </c>
       <c r="C126" t="str">
-        <v>wijn_rood_klein</v>
+        <v>kleine fles wijn rood</v>
+      </c>
+      <c r="D126" t="str">
+        <v>wijn rood klein</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -4654,10 +6864,28 @@
         <v>kleine_flesje_wijn_rose</v>
       </c>
       <c r="B127" t="str">
-        <v>kleine_fles_wijn_rose</v>
+        <v>kleine flesje wijn rose</v>
       </c>
       <c r="C127" t="str">
-        <v>wijn_rose_klein</v>
+        <v>kleine fles wijn rosé</v>
+      </c>
+      <c r="D127" t="str">
+        <v>wijn rosé klein</v>
+      </c>
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -4665,10 +6893,28 @@
         <v>kleine_flesje_wijn_wit</v>
       </c>
       <c r="B128" t="str">
-        <v>kleine_fles_wijn_wit</v>
+        <v>kleine flesje wijn wit</v>
       </c>
       <c r="C128" t="str">
-        <v>wijn_wit_klein</v>
+        <v>kleine fles wijn wit</v>
+      </c>
+      <c r="D128" t="str">
+        <v>wijn wit klein</v>
+      </c>
+      <c r="E128" t="str">
+        <v/>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -4684,13 +6930,49 @@
       <c r="D129" t="str">
         <v>appel_banaan_knijpzak</v>
       </c>
+      <c r="E129" t="str">
+        <v/>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
         <v>koffiebonen</v>
       </c>
       <c r="B130" t="str">
-        <v>koffie_bonen</v>
+        <v>koffiebonen</v>
+      </c>
+      <c r="C130" t="str">
+        <v>koffie bonen</v>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v/>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -4700,13 +6982,55 @@
       <c r="B131" t="str">
         <v>kokosroom</v>
       </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v/>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
         <v>kokosyoghurt</v>
       </c>
       <c r="B132" t="str">
-        <v>kokos_yoghurt</v>
+        <v>kokosyoghurt</v>
+      </c>
+      <c r="C132" t="str">
+        <v>kokos yoghurt</v>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v/>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -4716,6 +7040,27 @@
       <c r="B133" t="str">
         <v>verse_koriander</v>
       </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v/>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -4730,6 +7075,21 @@
       <c r="D134" t="str">
         <v>grenailles</v>
       </c>
+      <c r="E134" t="str">
+        <v/>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -4741,6 +7101,24 @@
       <c r="C135" t="str">
         <v>laurierblad</v>
       </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v/>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -4755,6 +7133,21 @@
       <c r="D136" t="str">
         <v>lentilles</v>
       </c>
+      <c r="E136" t="str">
+        <v/>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -4769,13 +7162,49 @@
       <c r="D137" t="str">
         <v>ooglensvloeistof</v>
       </c>
+      <c r="E137" t="str">
+        <v/>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
         <v>leo_go_mini</v>
       </c>
       <c r="B138" t="str">
+        <v>leo go mini</v>
+      </c>
+      <c r="C138" t="str">
         <v>leo</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v/>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -4788,6 +7217,24 @@
       <c r="C139" t="str">
         <v>kinnekessuiker</v>
       </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v/>
+      </c>
+      <c r="F139" t="str">
+        <v/>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+      <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -4814,16 +7261,37 @@
       <c r="H140" t="str">
         <v>teentjes_knoflook</v>
       </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
         <v>lookpoeder</v>
       </c>
       <c r="B141" t="str">
+        <v>lookpoeder</v>
+      </c>
+      <c r="C141" t="str">
         <v>knoflookpoeder</v>
       </c>
-      <c r="C141" t="str">
-        <v>granulaat</v>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v/>
+      </c>
+      <c r="F141" t="str">
+        <v/>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+      <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -4831,7 +7299,28 @@
         <v>loze_vinken</v>
       </c>
       <c r="B142" t="str">
-        <v>blinde_vinken</v>
+        <v>loze vinken</v>
+      </c>
+      <c r="C142" t="str">
+        <v>jules destrooper</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v/>
+      </c>
+      <c r="F142" t="str">
+        <v/>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+      <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -4841,6 +7330,27 @@
       <c r="B143" t="str">
         <v>maiskorrels</v>
       </c>
+      <c r="C143" t="str">
+        <v/>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143" t="str">
+        <v/>
+      </c>
+      <c r="F143" t="str">
+        <v/>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+      <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -4852,6 +7362,24 @@
       <c r="C144" t="str">
         <v>maiszetmeel</v>
       </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144" t="str">
+        <v/>
+      </c>
+      <c r="F144" t="str">
+        <v/>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+      <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -4860,6 +7388,27 @@
       <c r="B145" t="str">
         <v>mandarijn</v>
       </c>
+      <c r="C145" t="str">
+        <v/>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145" t="str">
+        <v/>
+      </c>
+      <c r="F145" t="str">
+        <v/>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+      <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -4868,13 +7417,55 @@
       <c r="B146" t="str">
         <v>mayonnaise</v>
       </c>
+      <c r="C146" t="str">
+        <v/>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+      <c r="E146" t="str">
+        <v/>
+      </c>
+      <c r="F146" t="str">
+        <v/>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+      <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
         <v>melk_halfvol</v>
       </c>
       <c r="B147" t="str">
-        <v>halfvolle_melk</v>
+        <v>melk halfvol</v>
+      </c>
+      <c r="C147" t="str">
+        <v>halfvolle melk</v>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+      <c r="E147" t="str">
+        <v/>
+      </c>
+      <c r="F147" t="str">
+        <v/>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+      <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -4882,7 +7473,28 @@
         <v>melk_mager</v>
       </c>
       <c r="B148" t="str">
-        <v>magere_melk</v>
+        <v>melk mager</v>
+      </c>
+      <c r="C148" t="str">
+        <v>magere melk</v>
+      </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
+      <c r="E148" t="str">
+        <v/>
+      </c>
+      <c r="F148" t="str">
+        <v/>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+      <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -4890,7 +7502,28 @@
         <v>melk_vol</v>
       </c>
       <c r="B149" t="str">
-        <v>volle_melk</v>
+        <v>melk vol</v>
+      </c>
+      <c r="C149" t="str">
+        <v>volle melk</v>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+      <c r="E149" t="str">
+        <v/>
+      </c>
+      <c r="F149" t="str">
+        <v/>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+      <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -4898,10 +7531,28 @@
         <v>melkchocolade_hazelnoten</v>
       </c>
       <c r="B150" t="str">
-        <v>melkchocolade_hazelnoot</v>
+        <v>melkchocolade hazelnoten</v>
       </c>
       <c r="C150" t="str">
-        <v>chocolade_hazelnoot</v>
+        <v>melkchocolade hazelnoot</v>
+      </c>
+      <c r="D150" t="str">
+        <v>chocolade hazelnoot</v>
+      </c>
+      <c r="E150" t="str">
+        <v/>
+      </c>
+      <c r="F150" t="str">
+        <v/>
+      </c>
+      <c r="G150" t="str">
+        <v/>
+      </c>
+      <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -4909,7 +7560,28 @@
         <v>melkchocolade_karamel_zeezout</v>
       </c>
       <c r="B151" t="str">
-        <v>karamel_zeezout_chocolade</v>
+        <v>melkchocolade karamel zeezout</v>
+      </c>
+      <c r="C151" t="str">
+        <v>karamel zeezout chocolade</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151" t="str">
+        <v/>
+      </c>
+      <c r="F151" t="str">
+        <v/>
+      </c>
+      <c r="G151" t="str">
+        <v/>
+      </c>
+      <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -4922,6 +7594,24 @@
       <c r="C152" t="str">
         <v>kleine_komkommers</v>
       </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+      <c r="E152" t="str">
+        <v/>
+      </c>
+      <c r="F152" t="str">
+        <v/>
+      </c>
+      <c r="G152" t="str">
+        <v/>
+      </c>
+      <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -4939,6 +7629,18 @@
       <c r="E153" t="str">
         <v>moules</v>
       </c>
+      <c r="F153" t="str">
+        <v/>
+      </c>
+      <c r="G153" t="str">
+        <v/>
+      </c>
+      <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -4947,6 +7649,27 @@
       <c r="B154" t="str">
         <v>dijonmmosterd</v>
       </c>
+      <c r="C154" t="str">
+        <v/>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+      <c r="E154" t="str">
+        <v/>
+      </c>
+      <c r="F154" t="str">
+        <v/>
+      </c>
+      <c r="G154" t="str">
+        <v/>
+      </c>
+      <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -4961,6 +7684,21 @@
       <c r="D155" t="str">
         <v>buffelmozarella</v>
       </c>
+      <c r="E155" t="str">
+        <v/>
+      </c>
+      <c r="F155" t="str">
+        <v/>
+      </c>
+      <c r="G155" t="str">
+        <v/>
+      </c>
+      <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -4969,6 +7707,27 @@
       <c r="B156" t="str">
         <v>verse_munt</v>
       </c>
+      <c r="C156" t="str">
+        <v/>
+      </c>
+      <c r="D156" t="str">
+        <v/>
+      </c>
+      <c r="E156" t="str">
+        <v/>
+      </c>
+      <c r="F156" t="str">
+        <v/>
+      </c>
+      <c r="G156" t="str">
+        <v/>
+      </c>
+      <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -4983,6 +7742,21 @@
       <c r="D157" t="str">
         <v>the_a_la_menthe</v>
       </c>
+      <c r="E157" t="str">
+        <v/>
+      </c>
+      <c r="F157" t="str">
+        <v/>
+      </c>
+      <c r="G157" t="str">
+        <v/>
+      </c>
+      <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -4994,6 +7768,24 @@
       <c r="C158" t="str">
         <v>indisch_broodmix</v>
       </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
+      <c r="E158" t="str">
+        <v/>
+      </c>
+      <c r="F158" t="str">
+        <v/>
+      </c>
+      <c r="G158" t="str">
+        <v/>
+      </c>
+      <c r="H158" t="str">
+        <v/>
+      </c>
+      <c r="I158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -5011,6 +7803,18 @@
       <c r="E159" t="str">
         <v>einoedels</v>
       </c>
+      <c r="F159" t="str">
+        <v/>
+      </c>
+      <c r="G159" t="str">
+        <v/>
+      </c>
+      <c r="H159" t="str">
+        <v/>
+      </c>
+      <c r="I159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -5022,6 +7826,24 @@
       <c r="C160" t="str">
         <v>kindnoedels</v>
       </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+      <c r="E160" t="str">
+        <v/>
+      </c>
+      <c r="F160" t="str">
+        <v/>
+      </c>
+      <c r="G160" t="str">
+        <v/>
+      </c>
+      <c r="H160" t="str">
+        <v/>
+      </c>
+      <c r="I160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -5039,6 +7861,18 @@
       <c r="E161" t="str">
         <v>gezouten_nootjes</v>
       </c>
+      <c r="F161" t="str">
+        <v/>
+      </c>
+      <c r="G161" t="str">
+        <v/>
+      </c>
+      <c r="H161" t="str">
+        <v/>
+      </c>
+      <c r="I161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -5056,6 +7890,18 @@
       <c r="E162" t="str">
         <v>geraspte_nootmuskaat</v>
       </c>
+      <c r="F162" t="str">
+        <v/>
+      </c>
+      <c r="G162" t="str">
+        <v/>
+      </c>
+      <c r="H162" t="str">
+        <v/>
+      </c>
+      <c r="I162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -5073,6 +7919,18 @@
       <c r="E163" t="str">
         <v>choco</v>
       </c>
+      <c r="F163" t="str">
+        <v/>
+      </c>
+      <c r="G163" t="str">
+        <v/>
+      </c>
+      <c r="H163" t="str">
+        <v/>
+      </c>
+      <c r="I163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -5090,6 +7948,18 @@
       <c r="E164" t="str">
         <v>holle_oesters</v>
       </c>
+      <c r="F164" t="str">
+        <v/>
+      </c>
+      <c r="G164" t="str">
+        <v/>
+      </c>
+      <c r="H164" t="str">
+        <v/>
+      </c>
+      <c r="I164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -5104,6 +7974,21 @@
       <c r="D165" t="str">
         <v>extra_vierge_olijfolie</v>
       </c>
+      <c r="E165" t="str">
+        <v/>
+      </c>
+      <c r="F165" t="str">
+        <v/>
+      </c>
+      <c r="G165" t="str">
+        <v/>
+      </c>
+      <c r="H165" t="str">
+        <v/>
+      </c>
+      <c r="I165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -5118,6 +8003,21 @@
       <c r="D166" t="str">
         <v>easter_eggs</v>
       </c>
+      <c r="E166" t="str">
+        <v/>
+      </c>
+      <c r="F166" t="str">
+        <v/>
+      </c>
+      <c r="G166" t="str">
+        <v/>
+      </c>
+      <c r="H166" t="str">
+        <v/>
+      </c>
+      <c r="I166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -5132,6 +8032,21 @@
       <c r="D167" t="str">
         <v>suikereitjes</v>
       </c>
+      <c r="E167" t="str">
+        <v/>
+      </c>
+      <c r="F167" t="str">
+        <v/>
+      </c>
+      <c r="G167" t="str">
+        <v/>
+      </c>
+      <c r="H167" t="str">
+        <v/>
+      </c>
+      <c r="I167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -5140,6 +8055,27 @@
       <c r="B168" t="str">
         <v>paksoy</v>
       </c>
+      <c r="C168" t="str">
+        <v/>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+      <c r="E168" t="str">
+        <v/>
+      </c>
+      <c r="F168" t="str">
+        <v/>
+      </c>
+      <c r="G168" t="str">
+        <v/>
+      </c>
+      <c r="H168" t="str">
+        <v/>
+      </c>
+      <c r="I168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -5154,6 +8090,21 @@
       <c r="D169" t="str">
         <v>crispy_breadcrumbs</v>
       </c>
+      <c r="E169" t="str">
+        <v/>
+      </c>
+      <c r="F169" t="str">
+        <v/>
+      </c>
+      <c r="G169" t="str">
+        <v/>
+      </c>
+      <c r="H169" t="str">
+        <v/>
+      </c>
+      <c r="I169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -5168,6 +8119,21 @@
       <c r="D170" t="str">
         <v>schrijfpapier</v>
       </c>
+      <c r="E170" t="str">
+        <v/>
+      </c>
+      <c r="F170" t="str">
+        <v/>
+      </c>
+      <c r="G170" t="str">
+        <v/>
+      </c>
+      <c r="H170" t="str">
+        <v/>
+      </c>
+      <c r="I170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -5176,6 +8142,27 @@
       <c r="B171" t="str">
         <v>rode_paprika</v>
       </c>
+      <c r="C171" t="str">
+        <v/>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+      <c r="E171" t="str">
+        <v/>
+      </c>
+      <c r="F171" t="str">
+        <v/>
+      </c>
+      <c r="G171" t="str">
+        <v/>
+      </c>
+      <c r="H171" t="str">
+        <v/>
+      </c>
+      <c r="I171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -5190,6 +8177,21 @@
       <c r="D172" t="str">
         <v>parel_suiker</v>
       </c>
+      <c r="E172" t="str">
+        <v/>
+      </c>
+      <c r="F172" t="str">
+        <v/>
+      </c>
+      <c r="G172" t="str">
+        <v/>
+      </c>
+      <c r="H172" t="str">
+        <v/>
+      </c>
+      <c r="I172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -5201,13 +8203,52 @@
       <c r="C173" t="str">
         <v>rauwe_ham</v>
       </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
+      <c r="E173" t="str">
+        <v/>
+      </c>
+      <c r="F173" t="str">
+        <v/>
+      </c>
+      <c r="G173" t="str">
+        <v/>
+      </c>
+      <c r="H173" t="str">
+        <v/>
+      </c>
+      <c r="I173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
         <v>parmezaan_blok</v>
       </c>
       <c r="B174" t="str">
-        <v>parmesan_blok</v>
+        <v>parmezaan blok</v>
+      </c>
+      <c r="C174" t="str">
+        <v>parmesan blok</v>
+      </c>
+      <c r="D174" t="str">
+        <v/>
+      </c>
+      <c r="E174" t="str">
+        <v/>
+      </c>
+      <c r="F174" t="str">
+        <v/>
+      </c>
+      <c r="G174" t="str">
+        <v/>
+      </c>
+      <c r="H174" t="str">
+        <v/>
+      </c>
+      <c r="I174" t="str">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -5215,7 +8256,28 @@
         <v>parmezaan_zakje</v>
       </c>
       <c r="B175" t="str">
-        <v>geraspte_parmezaan</v>
+        <v>parmezaan zakje</v>
+      </c>
+      <c r="C175" t="str">
+        <v>geraspte parmezaan</v>
+      </c>
+      <c r="D175" t="str">
+        <v/>
+      </c>
+      <c r="E175" t="str">
+        <v/>
+      </c>
+      <c r="F175" t="str">
+        <v/>
+      </c>
+      <c r="G175" t="str">
+        <v/>
+      </c>
+      <c r="H175" t="str">
+        <v/>
+      </c>
+      <c r="I175" t="str">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -5231,6 +8293,21 @@
       <c r="D176" t="str">
         <v>gezeefde_tomaten</v>
       </c>
+      <c r="E176" t="str">
+        <v/>
+      </c>
+      <c r="F176" t="str">
+        <v/>
+      </c>
+      <c r="G176" t="str">
+        <v/>
+      </c>
+      <c r="H176" t="str">
+        <v/>
+      </c>
+      <c r="I176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -5245,13 +8322,49 @@
       <c r="D177" t="str">
         <v>kinderpasta</v>
       </c>
+      <c r="E177" t="str">
+        <v/>
+      </c>
+      <c r="F177" t="str">
+        <v/>
+      </c>
+      <c r="G177" t="str">
+        <v/>
+      </c>
+      <c r="H177" t="str">
+        <v/>
+      </c>
+      <c r="I177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
         <v>pastasaus_pot</v>
       </c>
       <c r="B178" t="str">
-        <v>pot_pastasaus</v>
+        <v>pastasaus pot</v>
+      </c>
+      <c r="C178" t="str">
+        <v>pot pastasaus</v>
+      </c>
+      <c r="D178" t="str">
+        <v/>
+      </c>
+      <c r="E178" t="str">
+        <v/>
+      </c>
+      <c r="F178" t="str">
+        <v/>
+      </c>
+      <c r="G178" t="str">
+        <v/>
+      </c>
+      <c r="H178" t="str">
+        <v/>
+      </c>
+      <c r="I178" t="str">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -5259,7 +8372,28 @@
         <v>penne_pasta</v>
       </c>
       <c r="B179" t="str">
+        <v>penne pasta</v>
+      </c>
+      <c r="C179" t="str">
         <v>penne</v>
+      </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
+      <c r="E179" t="str">
+        <v/>
+      </c>
+      <c r="F179" t="str">
+        <v/>
+      </c>
+      <c r="G179" t="str">
+        <v/>
+      </c>
+      <c r="H179" t="str">
+        <v/>
+      </c>
+      <c r="I179" t="str">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -5267,7 +8401,28 @@
         <v>pepersalami</v>
       </c>
       <c r="B180" t="str">
-        <v>peper_salami</v>
+        <v>pepersalami</v>
+      </c>
+      <c r="C180" t="str">
+        <v>peper salami</v>
+      </c>
+      <c r="D180" t="str">
+        <v/>
+      </c>
+      <c r="E180" t="str">
+        <v/>
+      </c>
+      <c r="F180" t="str">
+        <v/>
+      </c>
+      <c r="G180" t="str">
+        <v/>
+      </c>
+      <c r="H180" t="str">
+        <v/>
+      </c>
+      <c r="I180" t="str">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -5286,6 +8441,18 @@
       <c r="E181" t="str">
         <v>suikervrije_cola</v>
       </c>
+      <c r="F181" t="str">
+        <v/>
+      </c>
+      <c r="G181" t="str">
+        <v/>
+      </c>
+      <c r="H181" t="str">
+        <v/>
+      </c>
+      <c r="I181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -5297,6 +8464,24 @@
       <c r="C182" t="str">
         <v>conference_peer</v>
       </c>
+      <c r="D182" t="str">
+        <v/>
+      </c>
+      <c r="E182" t="str">
+        <v/>
+      </c>
+      <c r="F182" t="str">
+        <v/>
+      </c>
+      <c r="G182" t="str">
+        <v/>
+      </c>
+      <c r="H182" t="str">
+        <v/>
+      </c>
+      <c r="I182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -5305,6 +8490,27 @@
       <c r="B183" t="str">
         <v>verse_peterselie</v>
       </c>
+      <c r="C183" t="str">
+        <v/>
+      </c>
+      <c r="D183" t="str">
+        <v/>
+      </c>
+      <c r="E183" t="str">
+        <v/>
+      </c>
+      <c r="F183" t="str">
+        <v/>
+      </c>
+      <c r="G183" t="str">
+        <v/>
+      </c>
+      <c r="H183" t="str">
+        <v/>
+      </c>
+      <c r="I183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -5319,13 +8525,49 @@
       <c r="D184" t="str">
         <v>chocoladekoek</v>
       </c>
+      <c r="E184" t="str">
+        <v/>
+      </c>
+      <c r="F184" t="str">
+        <v/>
+      </c>
+      <c r="G184" t="str">
+        <v/>
+      </c>
+      <c r="H184" t="str">
+        <v/>
+      </c>
+      <c r="I184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
         <v>pick_up_koekjes</v>
       </c>
       <c r="B185" t="str">
-        <v>pick_up</v>
+        <v>pick up koekjes</v>
+      </c>
+      <c r="C185" t="str">
+        <v>pick up</v>
+      </c>
+      <c r="D185" t="str">
+        <v/>
+      </c>
+      <c r="E185" t="str">
+        <v/>
+      </c>
+      <c r="F185" t="str">
+        <v/>
+      </c>
+      <c r="G185" t="str">
+        <v/>
+      </c>
+      <c r="H185" t="str">
+        <v/>
+      </c>
+      <c r="I185" t="str">
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -5353,6 +8595,9 @@
       <c r="H186" t="str">
         <v>pijpajuintje</v>
       </c>
+      <c r="I186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -5364,6 +8609,24 @@
       <c r="C187" t="str">
         <v>pinda_kaas</v>
       </c>
+      <c r="D187" t="str">
+        <v/>
+      </c>
+      <c r="E187" t="str">
+        <v/>
+      </c>
+      <c r="F187" t="str">
+        <v/>
+      </c>
+      <c r="G187" t="str">
+        <v/>
+      </c>
+      <c r="H187" t="str">
+        <v/>
+      </c>
+      <c r="I187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -5381,6 +8644,18 @@
       <c r="E188" t="str">
         <v>zachte_broodjes</v>
       </c>
+      <c r="F188" t="str">
+        <v/>
+      </c>
+      <c r="G188" t="str">
+        <v/>
+      </c>
+      <c r="H188" t="str">
+        <v/>
+      </c>
+      <c r="I188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -5395,6 +8670,21 @@
       <c r="D189" t="str">
         <v>frozen_pizza</v>
       </c>
+      <c r="E189" t="str">
+        <v/>
+      </c>
+      <c r="F189" t="str">
+        <v/>
+      </c>
+      <c r="G189" t="str">
+        <v/>
+      </c>
+      <c r="H189" t="str">
+        <v/>
+      </c>
+      <c r="I189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -5409,6 +8699,21 @@
       <c r="D190" t="str">
         <v>pizza_basis</v>
       </c>
+      <c r="E190" t="str">
+        <v/>
+      </c>
+      <c r="F190" t="str">
+        <v/>
+      </c>
+      <c r="G190" t="str">
+        <v/>
+      </c>
+      <c r="H190" t="str">
+        <v/>
+      </c>
+      <c r="I190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -5420,6 +8725,24 @@
       <c r="C191" t="str">
         <v>magere_kaas</v>
       </c>
+      <c r="D191" t="str">
+        <v/>
+      </c>
+      <c r="E191" t="str">
+        <v/>
+      </c>
+      <c r="F191" t="str">
+        <v/>
+      </c>
+      <c r="G191" t="str">
+        <v/>
+      </c>
+      <c r="H191" t="str">
+        <v/>
+      </c>
+      <c r="I191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -5434,6 +8757,21 @@
       <c r="D192" t="str">
         <v>wondpleister</v>
       </c>
+      <c r="E192" t="str">
+        <v/>
+      </c>
+      <c r="F192" t="str">
+        <v/>
+      </c>
+      <c r="G192" t="str">
+        <v/>
+      </c>
+      <c r="H192" t="str">
+        <v/>
+      </c>
+      <c r="I192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -5454,6 +8792,15 @@
       <c r="F193" t="str">
         <v>bloemsuiker</v>
       </c>
+      <c r="G193" t="str">
+        <v/>
+      </c>
+      <c r="H193" t="str">
+        <v/>
+      </c>
+      <c r="I193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -5465,6 +8812,24 @@
       <c r="C194" t="str">
         <v>preistengel</v>
       </c>
+      <c r="D194" t="str">
+        <v/>
+      </c>
+      <c r="E194" t="str">
+        <v/>
+      </c>
+      <c r="F194" t="str">
+        <v/>
+      </c>
+      <c r="G194" t="str">
+        <v/>
+      </c>
+      <c r="H194" t="str">
+        <v/>
+      </c>
+      <c r="I194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -5473,6 +8838,27 @@
       <c r="B195" t="str">
         <v>puddingpoeder</v>
       </c>
+      <c r="C195" t="str">
+        <v/>
+      </c>
+      <c r="D195" t="str">
+        <v/>
+      </c>
+      <c r="E195" t="str">
+        <v/>
+      </c>
+      <c r="F195" t="str">
+        <v/>
+      </c>
+      <c r="G195" t="str">
+        <v/>
+      </c>
+      <c r="H195" t="str">
+        <v/>
+      </c>
+      <c r="I195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -5487,13 +8873,49 @@
       <c r="D196" t="str">
         <v>portietoetje</v>
       </c>
+      <c r="E196" t="str">
+        <v/>
+      </c>
+      <c r="F196" t="str">
+        <v/>
+      </c>
+      <c r="G196" t="str">
+        <v/>
+      </c>
+      <c r="H196" t="str">
+        <v/>
+      </c>
+      <c r="I196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
         <v>pure_chocolade</v>
       </c>
       <c r="B197" t="str">
-        <v>donkere_chocolade</v>
+        <v>pure chocolade</v>
+      </c>
+      <c r="C197" t="str">
+        <v>donkere chocolade</v>
+      </c>
+      <c r="D197" t="str">
+        <v/>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v/>
+      </c>
+      <c r="G197" t="str">
+        <v/>
+      </c>
+      <c r="H197" t="str">
+        <v/>
+      </c>
+      <c r="I197" t="str">
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -5509,6 +8931,21 @@
       <c r="D198" t="str">
         <v>donker_bier</v>
       </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v/>
+      </c>
+      <c r="G198" t="str">
+        <v/>
+      </c>
+      <c r="H198" t="str">
+        <v/>
+      </c>
+      <c r="I198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -5517,6 +8954,27 @@
       <c r="B199" t="str">
         <v>radijs</v>
       </c>
+      <c r="C199" t="str">
+        <v/>
+      </c>
+      <c r="D199" t="str">
+        <v/>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v/>
+      </c>
+      <c r="G199" t="str">
+        <v/>
+      </c>
+      <c r="H199" t="str">
+        <v/>
+      </c>
+      <c r="I199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -5531,6 +8989,21 @@
       <c r="D200" t="str">
         <v>redbull</v>
       </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v/>
+      </c>
+      <c r="G200" t="str">
+        <v/>
+      </c>
+      <c r="H200" t="str">
+        <v/>
+      </c>
+      <c r="I200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -5551,6 +9024,15 @@
       <c r="F201" t="str">
         <v>bruine_rijst</v>
       </c>
+      <c r="G201" t="str">
+        <v/>
+      </c>
+      <c r="H201" t="str">
+        <v/>
+      </c>
+      <c r="I201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -5562,16 +9044,52 @@
       <c r="C202" t="str">
         <v>rice_paper</v>
       </c>
+      <c r="D202" t="str">
+        <v/>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v/>
+      </c>
+      <c r="G202" t="str">
+        <v/>
+      </c>
+      <c r="H202" t="str">
+        <v/>
+      </c>
+      <c r="I202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
         <v>rijstwafels</v>
       </c>
       <c r="B203" t="str">
+        <v>rijstwafels</v>
+      </c>
+      <c r="C203" t="str">
         <v>rijstwafel</v>
       </c>
-      <c r="C203" t="str">
-        <v>rice_cracker</v>
+      <c r="D203" t="str">
+        <v/>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v/>
+      </c>
+      <c r="G203" t="str">
+        <v/>
+      </c>
+      <c r="H203" t="str">
+        <v/>
+      </c>
+      <c r="I203" t="str">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -5584,6 +9102,24 @@
       <c r="C204" t="str">
         <v>rode_uien</v>
       </c>
+      <c r="D204" t="str">
+        <v/>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v/>
+      </c>
+      <c r="G204" t="str">
+        <v/>
+      </c>
+      <c r="H204" t="str">
+        <v/>
+      </c>
+      <c r="I204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -5592,19 +9128,55 @@
       <c r="B205" t="str">
         <v>currypasta</v>
       </c>
+      <c r="C205" t="str">
+        <v/>
+      </c>
+      <c r="D205" t="str">
+        <v/>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v/>
+      </c>
+      <c r="G205" t="str">
+        <v/>
+      </c>
+      <c r="H205" t="str">
+        <v/>
+      </c>
+      <c r="I205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
         <v>room_40_procent_vet</v>
       </c>
       <c r="B206" t="str">
-        <v>room_40</v>
+        <v>room 40 procent vet</v>
       </c>
       <c r="C206" t="str">
+        <v>room 40%</v>
+      </c>
+      <c r="D206" t="str">
         <v>kookroom</v>
       </c>
-      <c r="D206" t="str">
-        <v>slagroom_40</v>
+      <c r="E206" t="str">
+        <v>slagroom 40</v>
+      </c>
+      <c r="F206" t="str">
+        <v/>
+      </c>
+      <c r="G206" t="str">
+        <v/>
+      </c>
+      <c r="H206" t="str">
+        <v/>
+      </c>
+      <c r="I206" t="str">
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -5612,13 +9184,28 @@
         <v>room_7_procent_vet</v>
       </c>
       <c r="B207" t="str">
-        <v>room_7</v>
+        <v>room 7 procent vet</v>
       </c>
       <c r="C207" t="str">
+        <v>room 7%</v>
+      </c>
+      <c r="D207" t="str">
         <v>koffieroom</v>
       </c>
-      <c r="D207" t="str">
-        <v>kookroom_light</v>
+      <c r="E207" t="str">
+        <v>kookroom light</v>
+      </c>
+      <c r="F207" t="str">
+        <v/>
+      </c>
+      <c r="G207" t="str">
+        <v/>
+      </c>
+      <c r="H207" t="str">
+        <v/>
+      </c>
+      <c r="I207" t="str">
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -5637,6 +9224,18 @@
       <c r="E208" t="str">
         <v>fruityoghurt</v>
       </c>
+      <c r="F208" t="str">
+        <v/>
+      </c>
+      <c r="G208" t="str">
+        <v/>
+      </c>
+      <c r="H208" t="str">
+        <v/>
+      </c>
+      <c r="I208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -5645,6 +9244,27 @@
       <c r="B209" t="str">
         <v>verse_rozemarijn</v>
       </c>
+      <c r="C209" t="str">
+        <v/>
+      </c>
+      <c r="D209" t="str">
+        <v/>
+      </c>
+      <c r="E209" t="str">
+        <v/>
+      </c>
+      <c r="F209" t="str">
+        <v/>
+      </c>
+      <c r="G209" t="str">
+        <v/>
+      </c>
+      <c r="H209" t="str">
+        <v/>
+      </c>
+      <c r="I209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -5659,6 +9279,21 @@
       <c r="D210" t="str">
         <v>sultanarozijnen</v>
       </c>
+      <c r="E210" t="str">
+        <v/>
+      </c>
+      <c r="F210" t="str">
+        <v/>
+      </c>
+      <c r="G210" t="str">
+        <v/>
+      </c>
+      <c r="H210" t="str">
+        <v/>
+      </c>
+      <c r="I210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -5676,6 +9311,18 @@
       <c r="E211" t="str">
         <v>raketsla</v>
       </c>
+      <c r="F211" t="str">
+        <v/>
+      </c>
+      <c r="G211" t="str">
+        <v/>
+      </c>
+      <c r="H211" t="str">
+        <v/>
+      </c>
+      <c r="I211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -5687,13 +9334,52 @@
       <c r="C212" t="str">
         <v>bouillon</v>
       </c>
+      <c r="D212" t="str">
+        <v/>
+      </c>
+      <c r="E212" t="str">
+        <v/>
+      </c>
+      <c r="F212" t="str">
+        <v/>
+      </c>
+      <c r="G212" t="str">
+        <v/>
+      </c>
+      <c r="H212" t="str">
+        <v/>
+      </c>
+      <c r="I212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
         <v>sake</v>
       </c>
       <c r="B213" t="str">
-        <v>rijstwijn_sake</v>
+        <v>sake</v>
+      </c>
+      <c r="C213" t="str">
+        <v>rijstwijn sake</v>
+      </c>
+      <c r="D213" t="str">
+        <v/>
+      </c>
+      <c r="E213" t="str">
+        <v/>
+      </c>
+      <c r="F213" t="str">
+        <v/>
+      </c>
+      <c r="G213" t="str">
+        <v/>
+      </c>
+      <c r="H213" t="str">
+        <v/>
+      </c>
+      <c r="I213" t="str">
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -5709,6 +9395,21 @@
       <c r="D214" t="str">
         <v>milano_salami</v>
       </c>
+      <c r="E214" t="str">
+        <v/>
+      </c>
+      <c r="F214" t="str">
+        <v/>
+      </c>
+      <c r="G214" t="str">
+        <v/>
+      </c>
+      <c r="H214" t="str">
+        <v/>
+      </c>
+      <c r="I214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -5717,6 +9418,27 @@
       <c r="B215" t="str">
         <v>salami_kristof</v>
       </c>
+      <c r="C215" t="str">
+        <v/>
+      </c>
+      <c r="D215" t="str">
+        <v/>
+      </c>
+      <c r="E215" t="str">
+        <v/>
+      </c>
+      <c r="F215" t="str">
+        <v/>
+      </c>
+      <c r="G215" t="str">
+        <v/>
+      </c>
+      <c r="H215" t="str">
+        <v/>
+      </c>
+      <c r="I215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -5731,6 +9453,21 @@
       <c r="D216" t="str">
         <v>sriracha_mayo</v>
       </c>
+      <c r="E216" t="str">
+        <v/>
+      </c>
+      <c r="F216" t="str">
+        <v/>
+      </c>
+      <c r="G216" t="str">
+        <v/>
+      </c>
+      <c r="H216" t="str">
+        <v/>
+      </c>
+      <c r="I216" t="str">
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
@@ -5739,6 +9476,27 @@
       <c r="B217" t="str">
         <v>saus</v>
       </c>
+      <c r="C217" t="str">
+        <v/>
+      </c>
+      <c r="D217" t="str">
+        <v/>
+      </c>
+      <c r="E217" t="str">
+        <v/>
+      </c>
+      <c r="F217" t="str">
+        <v/>
+      </c>
+      <c r="G217" t="str">
+        <v/>
+      </c>
+      <c r="H217" t="str">
+        <v/>
+      </c>
+      <c r="I217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -5747,13 +9505,55 @@
       <c r="B218" t="str">
         <v>sandwich</v>
       </c>
+      <c r="C218" t="str">
+        <v/>
+      </c>
+      <c r="D218" t="str">
+        <v/>
+      </c>
+      <c r="E218" t="str">
+        <v/>
+      </c>
+      <c r="F218" t="str">
+        <v/>
+      </c>
+      <c r="G218" t="str">
+        <v/>
+      </c>
+      <c r="H218" t="str">
+        <v/>
+      </c>
+      <c r="I218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
         <v>sandwiches_zak</v>
       </c>
       <c r="B219" t="str">
-        <v>sandwich_zak</v>
+        <v>sandwiches zak</v>
+      </c>
+      <c r="C219" t="str">
+        <v>sandwich zak</v>
+      </c>
+      <c r="D219" t="str">
+        <v/>
+      </c>
+      <c r="E219" t="str">
+        <v/>
+      </c>
+      <c r="F219" t="str">
+        <v/>
+      </c>
+      <c r="G219" t="str">
+        <v/>
+      </c>
+      <c r="H219" t="str">
+        <v/>
+      </c>
+      <c r="I219" t="str">
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -5769,6 +9569,21 @@
       <c r="D220" t="str">
         <v>satekruidenmix</v>
       </c>
+      <c r="E220" t="str">
+        <v/>
+      </c>
+      <c r="F220" t="str">
+        <v/>
+      </c>
+      <c r="G220" t="str">
+        <v/>
+      </c>
+      <c r="H220" t="str">
+        <v/>
+      </c>
+      <c r="I220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -5777,6 +9592,27 @@
       <c r="B221" t="str">
         <v>scampi</v>
       </c>
+      <c r="C221" t="str">
+        <v/>
+      </c>
+      <c r="D221" t="str">
+        <v/>
+      </c>
+      <c r="E221" t="str">
+        <v/>
+      </c>
+      <c r="F221" t="str">
+        <v/>
+      </c>
+      <c r="G221" t="str">
+        <v/>
+      </c>
+      <c r="H221" t="str">
+        <v/>
+      </c>
+      <c r="I221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -5791,6 +9627,21 @@
       <c r="D222" t="str">
         <v>razor_blade</v>
       </c>
+      <c r="E222" t="str">
+        <v/>
+      </c>
+      <c r="F222" t="str">
+        <v/>
+      </c>
+      <c r="G222" t="str">
+        <v/>
+      </c>
+      <c r="H222" t="str">
+        <v/>
+      </c>
+      <c r="I222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -5805,13 +9656,49 @@
       <c r="D223" t="str">
         <v>shaving_foam</v>
       </c>
+      <c r="E223" t="str">
+        <v/>
+      </c>
+      <c r="F223" t="str">
+        <v/>
+      </c>
+      <c r="G223" t="str">
+        <v/>
+      </c>
+      <c r="H223" t="str">
+        <v/>
+      </c>
+      <c r="I223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
         <v>schnitzel</v>
       </c>
       <c r="B224" t="str">
+        <v>schnitzel</v>
+      </c>
+      <c r="C224" t="str">
         <v>kipschnitzel</v>
+      </c>
+      <c r="D224" t="str">
+        <v/>
+      </c>
+      <c r="E224" t="str">
+        <v/>
+      </c>
+      <c r="F224" t="str">
+        <v/>
+      </c>
+      <c r="G224" t="str">
+        <v/>
+      </c>
+      <c r="H224" t="str">
+        <v/>
+      </c>
+      <c r="I224" t="str">
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -5830,16 +9717,46 @@
       <c r="E225" t="str">
         <v>citrusfris</v>
       </c>
+      <c r="F225" t="str">
+        <v/>
+      </c>
+      <c r="G225" t="str">
+        <v/>
+      </c>
+      <c r="H225" t="str">
+        <v/>
+      </c>
+      <c r="I225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
         <v>seaweed_chips</v>
       </c>
       <c r="B226" t="str">
-        <v>zeewier_chips</v>
+        <v>seaweed chips</v>
       </c>
       <c r="C226" t="str">
-        <v>nori</v>
+        <v>zeewier chips</v>
+      </c>
+      <c r="D226" t="str">
+        <v/>
+      </c>
+      <c r="E226" t="str">
+        <v/>
+      </c>
+      <c r="F226" t="str">
+        <v/>
+      </c>
+      <c r="G226" t="str">
+        <v/>
+      </c>
+      <c r="H226" t="str">
+        <v/>
+      </c>
+      <c r="I226" t="str">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -5852,13 +9769,52 @@
       <c r="C227" t="str">
         <v>selderij</v>
       </c>
+      <c r="D227" t="str">
+        <v/>
+      </c>
+      <c r="E227" t="str">
+        <v/>
+      </c>
+      <c r="F227" t="str">
+        <v/>
+      </c>
+      <c r="G227" t="str">
+        <v/>
+      </c>
+      <c r="H227" t="str">
+        <v/>
+      </c>
+      <c r="I227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
         <v>sesamolie</v>
       </c>
       <c r="B228" t="str">
-        <v>sesam_olie</v>
+        <v>sesamolie</v>
+      </c>
+      <c r="C228" t="str">
+        <v>sesam olie</v>
+      </c>
+      <c r="D228" t="str">
+        <v/>
+      </c>
+      <c r="E228" t="str">
+        <v/>
+      </c>
+      <c r="F228" t="str">
+        <v/>
+      </c>
+      <c r="G228" t="str">
+        <v/>
+      </c>
+      <c r="H228" t="str">
+        <v/>
+      </c>
+      <c r="I228" t="str">
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -5874,6 +9830,21 @@
       <c r="D229" t="str">
         <v>shampooing</v>
       </c>
+      <c r="E229" t="str">
+        <v/>
+      </c>
+      <c r="F229" t="str">
+        <v/>
+      </c>
+      <c r="G229" t="str">
+        <v/>
+      </c>
+      <c r="H229" t="str">
+        <v/>
+      </c>
+      <c r="I229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -5888,6 +9859,21 @@
       <c r="D230" t="str">
         <v>sjalotjes</v>
       </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -5896,6 +9882,27 @@
       <c r="B231" t="str">
         <v>soja_saus</v>
       </c>
+      <c r="C231" t="str">
+        <v/>
+      </c>
+      <c r="D231" t="str">
+        <v/>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -5910,6 +9917,21 @@
       <c r="D232" t="str">
         <v>buikspek</v>
       </c>
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -5921,6 +9943,24 @@
       <c r="C233" t="str">
         <v>spekblokje</v>
       </c>
+      <c r="D233" t="str">
+        <v/>
+      </c>
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -5932,6 +9972,24 @@
       <c r="C234" t="str">
         <v>spek</v>
       </c>
+      <c r="D234" t="str">
+        <v/>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -5943,6 +10001,24 @@
       <c r="C235" t="str">
         <v>bloem_spelt</v>
       </c>
+      <c r="D235" t="str">
+        <v/>
+      </c>
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -5960,16 +10036,46 @@
       <c r="E236" t="str">
         <v>epinards</v>
       </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
         <v>spirelli_pasta</v>
       </c>
       <c r="B237" t="str">
-        <v>pasta</v>
+        <v>spirelli pasta</v>
       </c>
       <c r="C237" t="str">
         <v>spirelli</v>
+      </c>
+      <c r="D237" t="str">
+        <v/>
+      </c>
+      <c r="E237" t="str">
+        <v/>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -5982,6 +10088,24 @@
       <c r="C238" t="str">
         <v>anti_kleefspray</v>
       </c>
+      <c r="D238" t="str">
+        <v/>
+      </c>
+      <c r="E238" t="str">
+        <v/>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -5996,6 +10120,21 @@
       <c r="D239" t="str">
         <v>olijfolie</v>
       </c>
+      <c r="E239" t="str">
+        <v/>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -6010,6 +10149,21 @@
       <c r="D240" t="str">
         <v>rode_chilisaus</v>
       </c>
+      <c r="E240" t="str">
+        <v/>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -6027,6 +10181,18 @@
       <c r="E241" t="str">
         <v>langbrood</v>
       </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -6041,13 +10207,49 @@
       <c r="D242" t="str">
         <v>witte_suiker</v>
       </c>
+      <c r="E242" t="str">
+        <v/>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
         <v>suikerwafel</v>
       </c>
       <c r="B243" t="str">
+        <v>suikerwafel</v>
+      </c>
+      <c r="C243" t="str">
         <v>suikerwafels</v>
+      </c>
+      <c r="D243" t="str">
+        <v/>
+      </c>
+      <c r="E243" t="str">
+        <v/>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -6060,6 +10262,24 @@
       <c r="C244" t="str">
         <v>suikerklontjes</v>
       </c>
+      <c r="D244" t="str">
+        <v/>
+      </c>
+      <c r="E244" t="str">
+        <v/>
+      </c>
+      <c r="F244" t="str">
+        <v/>
+      </c>
+      <c r="G244" t="str">
+        <v/>
+      </c>
+      <c r="H244" t="str">
+        <v/>
+      </c>
+      <c r="I244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -6074,6 +10294,21 @@
       <c r="D245" t="str">
         <v>caloriearm_suiker</v>
       </c>
+      <c r="E245" t="str">
+        <v/>
+      </c>
+      <c r="F245" t="str">
+        <v/>
+      </c>
+      <c r="G245" t="str">
+        <v/>
+      </c>
+      <c r="H245" t="str">
+        <v/>
+      </c>
+      <c r="I245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -6085,13 +10320,52 @@
       <c r="C246" t="str">
         <v>indisch_kruidenpasta</v>
       </c>
+      <c r="D246" t="str">
+        <v/>
+      </c>
+      <c r="E246" t="str">
+        <v/>
+      </c>
+      <c r="F246" t="str">
+        <v/>
+      </c>
+      <c r="G246" t="str">
+        <v/>
+      </c>
+      <c r="H246" t="str">
+        <v/>
+      </c>
+      <c r="I246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
         <v>tandoori_poeder</v>
       </c>
       <c r="B247" t="str">
+        <v>tandoori poeder</v>
+      </c>
+      <c r="C247" t="str">
         <v>tandoori</v>
+      </c>
+      <c r="D247" t="str">
+        <v/>
+      </c>
+      <c r="E247" t="str">
+        <v/>
+      </c>
+      <c r="F247" t="str">
+        <v/>
+      </c>
+      <c r="G247" t="str">
+        <v/>
+      </c>
+      <c r="H247" t="str">
+        <v/>
+      </c>
+      <c r="I247" t="str">
+        <v/>
       </c>
     </row>
     <row r="248">
@@ -6107,6 +10381,21 @@
       <c r="D248" t="str">
         <v>agave</v>
       </c>
+      <c r="E248" t="str">
+        <v/>
+      </c>
+      <c r="F248" t="str">
+        <v/>
+      </c>
+      <c r="G248" t="str">
+        <v/>
+      </c>
+      <c r="H248" t="str">
+        <v/>
+      </c>
+      <c r="I248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -6115,6 +10404,27 @@
       <c r="B249" t="str">
         <v>verse_tijm</v>
       </c>
+      <c r="C249" t="str">
+        <v/>
+      </c>
+      <c r="D249" t="str">
+        <v/>
+      </c>
+      <c r="E249" t="str">
+        <v/>
+      </c>
+      <c r="F249" t="str">
+        <v/>
+      </c>
+      <c r="G249" t="str">
+        <v/>
+      </c>
+      <c r="H249" t="str">
+        <v/>
+      </c>
+      <c r="I249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -6129,19 +10439,49 @@
       <c r="D250" t="str">
         <v>kleenex</v>
       </c>
+      <c r="E250" t="str">
+        <v/>
+      </c>
+      <c r="F250" t="str">
+        <v/>
+      </c>
+      <c r="G250" t="str">
+        <v/>
+      </c>
+      <c r="H250" t="str">
+        <v/>
+      </c>
+      <c r="I250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
         <v>toastjes</v>
       </c>
       <c r="B251" t="str">
+        <v>toastjes</v>
+      </c>
+      <c r="C251" t="str">
         <v>toast</v>
       </c>
-      <c r="C251" t="str">
-        <v>beschuit</v>
-      </c>
       <c r="D251" t="str">
-        <v>biscotte</v>
+        <v/>
+      </c>
+      <c r="E251" t="str">
+        <v/>
+      </c>
+      <c r="F251" t="str">
+        <v/>
+      </c>
+      <c r="G251" t="str">
+        <v/>
+      </c>
+      <c r="H251" t="str">
+        <v/>
+      </c>
+      <c r="I251" t="str">
+        <v/>
       </c>
     </row>
     <row r="252">
@@ -6154,6 +10494,24 @@
       <c r="C252" t="str">
         <v>toilet_paper</v>
       </c>
+      <c r="D252" t="str">
+        <v/>
+      </c>
+      <c r="E252" t="str">
+        <v/>
+      </c>
+      <c r="F252" t="str">
+        <v/>
+      </c>
+      <c r="G252" t="str">
+        <v/>
+      </c>
+      <c r="H252" t="str">
+        <v/>
+      </c>
+      <c r="I252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -6165,6 +10523,24 @@
       <c r="C253" t="str">
         <v>tomaatje</v>
       </c>
+      <c r="D253" t="str">
+        <v/>
+      </c>
+      <c r="E253" t="str">
+        <v/>
+      </c>
+      <c r="F253" t="str">
+        <v/>
+      </c>
+      <c r="G253" t="str">
+        <v/>
+      </c>
+      <c r="H253" t="str">
+        <v/>
+      </c>
+      <c r="I253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -6173,6 +10549,27 @@
       <c r="B254" t="str">
         <v>geconcentreerde_tomatenpuree</v>
       </c>
+      <c r="C254" t="str">
+        <v/>
+      </c>
+      <c r="D254" t="str">
+        <v/>
+      </c>
+      <c r="E254" t="str">
+        <v/>
+      </c>
+      <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+      <c r="H254" t="str">
+        <v/>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
@@ -6187,6 +10584,21 @@
       <c r="D255" t="str">
         <v>indian_tonic</v>
       </c>
+      <c r="E255" t="str">
+        <v/>
+      </c>
+      <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
@@ -6201,6 +10613,21 @@
       <c r="D256" t="str">
         <v>dishwasher_tablets</v>
       </c>
+      <c r="E256" t="str">
+        <v/>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
+        <v/>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
@@ -6212,6 +10639,24 @@
       <c r="C257" t="str">
         <v>vanilleextract</v>
       </c>
+      <c r="D257" t="str">
+        <v/>
+      </c>
+      <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
@@ -6220,6 +10665,27 @@
       <c r="B258" t="str">
         <v>vanillestokje</v>
       </c>
+      <c r="C258" t="str">
+        <v/>
+      </c>
+      <c r="D258" t="str">
+        <v/>
+      </c>
+      <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+      <c r="H258" t="str">
+        <v/>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
@@ -6234,6 +10700,21 @@
       <c r="D259" t="str">
         <v>suiker_met_vanille</v>
       </c>
+      <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+      <c r="H259" t="str">
+        <v/>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
@@ -6242,6 +10723,27 @@
       <c r="B260" t="str">
         <v>frieten</v>
       </c>
+      <c r="C260" t="str">
+        <v/>
+      </c>
+      <c r="D260" t="str">
+        <v/>
+      </c>
+      <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
@@ -6250,6 +10752,27 @@
       <c r="B261" t="str">
         <v>gist</v>
       </c>
+      <c r="C261" t="str">
+        <v/>
+      </c>
+      <c r="D261" t="str">
+        <v/>
+      </c>
+      <c r="E261" t="str">
+        <v/>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
@@ -6264,6 +10787,21 @@
       <c r="D262" t="str">
         <v>lasagnevellen_vers</v>
       </c>
+      <c r="E262" t="str">
+        <v/>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+      <c r="H262" t="str">
+        <v/>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
@@ -6272,13 +10810,55 @@
       <c r="B263" t="str">
         <v>bouiillon</v>
       </c>
+      <c r="C263" t="str">
+        <v/>
+      </c>
+      <c r="D263" t="str">
+        <v/>
+      </c>
+      <c r="E263" t="str">
+        <v/>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v/>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
         <v>vuilzakken</v>
       </c>
       <c r="B264" t="str">
+        <v>vuilzakken</v>
+      </c>
+      <c r="C264" t="str">
         <v>afvalzakken</v>
+      </c>
+      <c r="D264" t="str">
+        <v/>
+      </c>
+      <c r="E264" t="str">
+        <v/>
+      </c>
+      <c r="F264" t="str">
+        <v/>
+      </c>
+      <c r="G264" t="str">
+        <v/>
+      </c>
+      <c r="H264" t="str">
+        <v/>
+      </c>
+      <c r="I264" t="str">
+        <v/>
       </c>
     </row>
     <row r="265">
@@ -6291,6 +10871,24 @@
       <c r="C265" t="str">
         <v>noten</v>
       </c>
+      <c r="D265" t="str">
+        <v/>
+      </c>
+      <c r="E265" t="str">
+        <v/>
+      </c>
+      <c r="F265" t="str">
+        <v/>
+      </c>
+      <c r="G265" t="str">
+        <v/>
+      </c>
+      <c r="H265" t="str">
+        <v/>
+      </c>
+      <c r="I265" t="str">
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
@@ -6305,6 +10903,21 @@
       <c r="D266" t="str">
         <v>lessive</v>
       </c>
+      <c r="E266" t="str">
+        <v/>
+      </c>
+      <c r="F266" t="str">
+        <v/>
+      </c>
+      <c r="G266" t="str">
+        <v/>
+      </c>
+      <c r="H266" t="str">
+        <v/>
+      </c>
+      <c r="I266" t="str">
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
@@ -6319,6 +10932,21 @@
       <c r="D267" t="str">
         <v>assouplissant</v>
       </c>
+      <c r="E267" t="str">
+        <v/>
+      </c>
+      <c r="F267" t="str">
+        <v/>
+      </c>
+      <c r="G267" t="str">
+        <v/>
+      </c>
+      <c r="H267" t="str">
+        <v/>
+      </c>
+      <c r="I267" t="str">
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
@@ -6333,6 +10961,21 @@
       <c r="D268" t="str">
         <v>cotton_buds</v>
       </c>
+      <c r="E268" t="str">
+        <v/>
+      </c>
+      <c r="F268" t="str">
+        <v/>
+      </c>
+      <c r="G268" t="str">
+        <v/>
+      </c>
+      <c r="H268" t="str">
+        <v/>
+      </c>
+      <c r="I268" t="str">
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
@@ -6347,6 +10990,21 @@
       <c r="D269" t="str">
         <v>sanitairblok</v>
       </c>
+      <c r="E269" t="str">
+        <v/>
+      </c>
+      <c r="F269" t="str">
+        <v/>
+      </c>
+      <c r="G269" t="str">
+        <v/>
+      </c>
+      <c r="H269" t="str">
+        <v/>
+      </c>
+      <c r="I269" t="str">
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
@@ -6358,6 +11016,24 @@
       <c r="C270" t="str">
         <v>toilet_reiniger</v>
       </c>
+      <c r="D270" t="str">
+        <v/>
+      </c>
+      <c r="E270" t="str">
+        <v/>
+      </c>
+      <c r="F270" t="str">
+        <v/>
+      </c>
+      <c r="G270" t="str">
+        <v/>
+      </c>
+      <c r="H270" t="str">
+        <v/>
+      </c>
+      <c r="I270" t="str">
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
@@ -6366,13 +11042,55 @@
       <c r="B271" t="str">
         <v>witlof</v>
       </c>
+      <c r="C271" t="str">
+        <v/>
+      </c>
+      <c r="D271" t="str">
+        <v/>
+      </c>
+      <c r="E271" t="str">
+        <v/>
+      </c>
+      <c r="F271" t="str">
+        <v/>
+      </c>
+      <c r="G271" t="str">
+        <v/>
+      </c>
+      <c r="H271" t="str">
+        <v/>
+      </c>
+      <c r="I271" t="str">
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
         <v>witte_peper_poeder</v>
       </c>
       <c r="B272" t="str">
-        <v>witte_peper_gemalen</v>
+        <v>witte peper poeder</v>
+      </c>
+      <c r="C272" t="str">
+        <v>witte peper gemalen</v>
+      </c>
+      <c r="D272" t="str">
+        <v/>
+      </c>
+      <c r="E272" t="str">
+        <v/>
+      </c>
+      <c r="F272" t="str">
+        <v/>
+      </c>
+      <c r="G272" t="str">
+        <v/>
+      </c>
+      <c r="H272" t="str">
+        <v/>
+      </c>
+      <c r="I272" t="str">
+        <v/>
       </c>
     </row>
     <row r="273">
@@ -6380,7 +11098,28 @@
         <v>witte_peperbollen</v>
       </c>
       <c r="B273" t="str">
-        <v>witte_peper</v>
+        <v>witte peperbollen</v>
+      </c>
+      <c r="C273" t="str">
+        <v>witte peper</v>
+      </c>
+      <c r="D273" t="str">
+        <v/>
+      </c>
+      <c r="E273" t="str">
+        <v/>
+      </c>
+      <c r="F273" t="str">
+        <v/>
+      </c>
+      <c r="G273" t="str">
+        <v/>
+      </c>
+      <c r="H273" t="str">
+        <v/>
+      </c>
+      <c r="I273" t="str">
+        <v/>
       </c>
     </row>
     <row r="274">
@@ -6390,6 +11129,27 @@
       <c r="B274" t="str">
         <v>wijn</v>
       </c>
+      <c r="C274" t="str">
+        <v/>
+      </c>
+      <c r="D274" t="str">
+        <v/>
+      </c>
+      <c r="E274" t="str">
+        <v/>
+      </c>
+      <c r="F274" t="str">
+        <v/>
+      </c>
+      <c r="G274" t="str">
+        <v/>
+      </c>
+      <c r="H274" t="str">
+        <v/>
+      </c>
+      <c r="I274" t="str">
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
@@ -6404,6 +11164,21 @@
       <c r="D275" t="str">
         <v>gedistilleerd</v>
       </c>
+      <c r="E275" t="str">
+        <v/>
+      </c>
+      <c r="F275" t="str">
+        <v/>
+      </c>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
@@ -6415,6 +11190,24 @@
       <c r="C276" t="str">
         <v>worstje</v>
       </c>
+      <c r="D276" t="str">
+        <v/>
+      </c>
+      <c r="E276" t="str">
+        <v/>
+      </c>
+      <c r="F276" t="str">
+        <v/>
+      </c>
+      <c r="G276" t="str">
+        <v/>
+      </c>
+      <c r="H276" t="str">
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
@@ -6426,6 +11219,24 @@
       <c r="C277" t="str">
         <v>saucijzenbroodje</v>
       </c>
+      <c r="D277" t="str">
+        <v/>
+      </c>
+      <c r="E277" t="str">
+        <v/>
+      </c>
+      <c r="F277" t="str">
+        <v/>
+      </c>
+      <c r="G277" t="str">
+        <v/>
+      </c>
+      <c r="H277" t="str">
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
@@ -6443,6 +11254,18 @@
       <c r="E278" t="str">
         <v>worteltjes</v>
       </c>
+      <c r="F278" t="str">
+        <v/>
+      </c>
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
@@ -6460,6 +11283,18 @@
       <c r="E279" t="str">
         <v>carotte</v>
       </c>
+      <c r="F279" t="str">
+        <v/>
+      </c>
+      <c r="G279" t="str">
+        <v/>
+      </c>
+      <c r="H279" t="str">
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
@@ -6468,6 +11303,27 @@
       <c r="B280" t="str">
         <v>tortilla</v>
       </c>
+      <c r="C280" t="str">
+        <v/>
+      </c>
+      <c r="D280" t="str">
+        <v/>
+      </c>
+      <c r="E280" t="str">
+        <v/>
+      </c>
+      <c r="F280" t="str">
+        <v/>
+      </c>
+      <c r="G280" t="str">
+        <v/>
+      </c>
+      <c r="H280" t="str">
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
@@ -6476,6 +11332,27 @@
       <c r="B281" t="str">
         <v>griekse_yoghurt</v>
       </c>
+      <c r="C281" t="str">
+        <v/>
+      </c>
+      <c r="D281" t="str">
+        <v/>
+      </c>
+      <c r="E281" t="str">
+        <v/>
+      </c>
+      <c r="F281" t="str">
+        <v/>
+      </c>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
@@ -6484,6 +11361,27 @@
       <c r="B282" t="str">
         <v>zalm_filet</v>
       </c>
+      <c r="C282" t="str">
+        <v/>
+      </c>
+      <c r="D282" t="str">
+        <v/>
+      </c>
+      <c r="E282" t="str">
+        <v/>
+      </c>
+      <c r="F282" t="str">
+        <v/>
+      </c>
+      <c r="G282" t="str">
+        <v/>
+      </c>
+      <c r="H282" t="str">
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
@@ -6501,6 +11399,18 @@
       <c r="E283" t="str">
         <v>zelfrijzen_bakmeel</v>
       </c>
+      <c r="F283" t="str">
+        <v/>
+      </c>
+      <c r="G283" t="str">
+        <v/>
+      </c>
+      <c r="H283" t="str">
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
@@ -6518,6 +11428,18 @@
       <c r="E284" t="str">
         <v>papier_aluminium</v>
       </c>
+      <c r="F284" t="str">
+        <v/>
+      </c>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
@@ -6526,6 +11448,27 @@
       <c r="B285" t="str">
         <v>zilverui</v>
       </c>
+      <c r="C285" t="str">
+        <v/>
+      </c>
+      <c r="D285" t="str">
+        <v/>
+      </c>
+      <c r="E285" t="str">
+        <v/>
+      </c>
+      <c r="F285" t="str">
+        <v/>
+      </c>
+      <c r="G285" t="str">
+        <v/>
+      </c>
+      <c r="H285" t="str">
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -6540,6 +11483,21 @@
       <c r="D286" t="str">
         <v>zoete_aardappels</v>
       </c>
+      <c r="E286" t="str">
+        <v/>
+      </c>
+      <c r="F286" t="str">
+        <v/>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
@@ -6560,6 +11518,15 @@
       <c r="F287" t="str">
         <v>sel</v>
       </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
@@ -6574,6 +11541,21 @@
       <c r="D288" t="str">
         <v>sel_lave_vaisselle</v>
       </c>
+      <c r="E288" t="str">
+        <v/>
+      </c>
+      <c r="F288" t="str">
+        <v/>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
@@ -6582,6 +11564,27 @@
       <c r="B289" t="str">
         <v>sour_cream</v>
       </c>
+      <c r="C289" t="str">
+        <v/>
+      </c>
+      <c r="D289" t="str">
+        <v/>
+      </c>
+      <c r="E289" t="str">
+        <v/>
+      </c>
+      <c r="F289" t="str">
+        <v/>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
@@ -6590,18 +11593,582 @@
       <c r="B290" t="str">
         <v>naturel_zoetmiddel</v>
       </c>
+      <c r="C290" t="str">
+        <v/>
+      </c>
+      <c r="D290" t="str">
+        <v/>
+      </c>
+      <c r="E290" t="str">
+        <v/>
+      </c>
+      <c r="F290" t="str">
+        <v/>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
         <v>zwarte_peperbollen</v>
       </c>
       <c r="B291" t="str">
-        <v>zwarte_peper</v>
+        <v>zwarte peperbollen</v>
+      </c>
+      <c r="C291" t="str">
+        <v>zwarte peper</v>
+      </c>
+      <c r="D291" t="str">
+        <v/>
+      </c>
+      <c r="E291" t="str">
+        <v/>
+      </c>
+      <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>raffaello</v>
+      </c>
+      <c r="B292" t="str">
+        <v>raffaello</v>
+      </c>
+      <c r="C292" t="str">
+        <v/>
+      </c>
+      <c r="D292" t="str">
+        <v/>
+      </c>
+      <c r="E292" t="str">
+        <v/>
+      </c>
+      <c r="F292" t="str">
+        <v/>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>suikerspin</v>
+      </c>
+      <c r="B293" t="str">
+        <v>suikerspin</v>
+      </c>
+      <c r="C293" t="str">
+        <v/>
+      </c>
+      <c r="D293" t="str">
+        <v/>
+      </c>
+      <c r="E293" t="str">
+        <v/>
+      </c>
+      <c r="F293" t="str">
+        <v/>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>chips_croky_paprika_rings</v>
+      </c>
+      <c r="B294" t="str">
+        <v>chips croky paprika rings</v>
+      </c>
+      <c r="C294" t="str">
+        <v>croky paprika rings</v>
+      </c>
+      <c r="D294" t="str">
+        <v>croky chips paprika</v>
+      </c>
+      <c r="E294" t="str">
+        <v/>
+      </c>
+      <c r="F294" t="str">
+        <v/>
+      </c>
+      <c r="G294" t="str">
+        <v/>
+      </c>
+      <c r="H294" t="str">
+        <v/>
+      </c>
+      <c r="I294" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>chips_paprika</v>
+      </c>
+      <c r="B295" t="str">
+        <v>chips paprika</v>
+      </c>
+      <c r="C295" t="str">
+        <v>paprika chips</v>
+      </c>
+      <c r="D295" t="str">
+        <v/>
+      </c>
+      <c r="E295" t="str">
+        <v/>
+      </c>
+      <c r="F295" t="str">
+        <v/>
+      </c>
+      <c r="G295" t="str">
+        <v/>
+      </c>
+      <c r="H295" t="str">
+        <v/>
+      </c>
+      <c r="I295" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>chips_pickles</v>
+      </c>
+      <c r="B296" t="str">
+        <v>chips pickles</v>
+      </c>
+      <c r="C296" t="str">
+        <v>pickles chips</v>
+      </c>
+      <c r="D296" t="str">
+        <v>augurken chips</v>
+      </c>
+      <c r="E296" t="str">
+        <v/>
+      </c>
+      <c r="F296" t="str">
+        <v/>
+      </c>
+      <c r="G296" t="str">
+        <v/>
+      </c>
+      <c r="H296" t="str">
+        <v/>
+      </c>
+      <c r="I296" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>chips_salt_and_vinegar</v>
+      </c>
+      <c r="B297" t="str">
+        <v>chips salt and vinegar</v>
+      </c>
+      <c r="C297" t="str">
+        <v>salt and vinegar chips</v>
+      </c>
+      <c r="D297" t="str">
+        <v>zout azijn chips</v>
+      </c>
+      <c r="E297" t="str">
+        <v/>
+      </c>
+      <c r="F297" t="str">
+        <v/>
+      </c>
+      <c r="G297" t="str">
+        <v/>
+      </c>
+      <c r="H297" t="str">
+        <v/>
+      </c>
+      <c r="I297" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>chips_zout</v>
+      </c>
+      <c r="B298" t="str">
+        <v>chips zout</v>
+      </c>
+      <c r="C298" t="str">
+        <v>zoute chips</v>
+      </c>
+      <c r="D298" t="str">
+        <v/>
+      </c>
+      <c r="E298" t="str">
+        <v/>
+      </c>
+      <c r="F298" t="str">
+        <v/>
+      </c>
+      <c r="G298" t="str">
+        <v/>
+      </c>
+      <c r="H298" t="str">
+        <v/>
+      </c>
+      <c r="I298" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>confituur</v>
+      </c>
+      <c r="B299" t="str">
+        <v>confituur</v>
+      </c>
+      <c r="C299" t="str">
+        <v>jam</v>
+      </c>
+      <c r="D299" t="str">
+        <v>confiture</v>
+      </c>
+      <c r="E299" t="str">
+        <v>fruitbeleg</v>
+      </c>
+      <c r="F299" t="str">
+        <v/>
+      </c>
+      <c r="G299" t="str">
+        <v/>
+      </c>
+      <c r="H299" t="str">
+        <v/>
+      </c>
+      <c r="I299" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>coquilles</v>
+      </c>
+      <c r="B300" t="str">
+        <v>coquilles</v>
+      </c>
+      <c r="C300" t="str">
+        <v>sint-jakobsschelpen</v>
+      </c>
+      <c r="D300" t="str">
+        <v>jakobsschelpen</v>
+      </c>
+      <c r="E300" t="str">
+        <v/>
+      </c>
+      <c r="F300" t="str">
+        <v/>
+      </c>
+      <c r="G300" t="str">
+        <v/>
+      </c>
+      <c r="H300" t="str">
+        <v/>
+      </c>
+      <c r="I300" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>gerookte_zalmhaasje</v>
+      </c>
+      <c r="B301" t="str">
+        <v>gerookte zalmhaasje</v>
+      </c>
+      <c r="C301" t="str">
+        <v>gerookte zalm</v>
+      </c>
+      <c r="D301" t="str">
+        <v>rookzalm</v>
+      </c>
+      <c r="E301" t="str">
+        <v>zalmhaasje</v>
+      </c>
+      <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
+      <c r="I301" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>huishoudfolie</v>
+      </c>
+      <c r="B302" t="str">
+        <v>huishoudfolie</v>
+      </c>
+      <c r="C302" t="str">
+        <v>aluminiumfolie</v>
+      </c>
+      <c r="D302" t="str">
+        <v>afdeklfolie</v>
+      </c>
+      <c r="E302" t="str">
+        <v>vershoudfolie</v>
+      </c>
+      <c r="F302" t="str">
+        <v/>
+      </c>
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
+      <c r="I302" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>pompoen</v>
+      </c>
+      <c r="B303" t="str">
+        <v>pompoen</v>
+      </c>
+      <c r="C303" t="str">
+        <v>pumpkin</v>
+      </c>
+      <c r="D303" t="str">
+        <v>pompoenstuk</v>
+      </c>
+      <c r="E303" t="str">
+        <v/>
+      </c>
+      <c r="F303" t="str">
+        <v/>
+      </c>
+      <c r="G303" t="str">
+        <v/>
+      </c>
+      <c r="H303" t="str">
+        <v/>
+      </c>
+      <c r="I303" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>smeerboter</v>
+      </c>
+      <c r="B304" t="str">
+        <v>smeerboter</v>
+      </c>
+      <c r="C304" t="str">
+        <v>boter om te smeren</v>
+      </c>
+      <c r="D304" t="str">
+        <v>roomboter kuip</v>
+      </c>
+      <c r="E304" t="str">
+        <v/>
+      </c>
+      <c r="F304" t="str">
+        <v/>
+      </c>
+      <c r="G304" t="str">
+        <v/>
+      </c>
+      <c r="H304" t="str">
+        <v/>
+      </c>
+      <c r="I304" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>speculoospasta</v>
+      </c>
+      <c r="B305" t="str">
+        <v>speculoospasta</v>
+      </c>
+      <c r="C305" t="str">
+        <v>speculoos pasta</v>
+      </c>
+      <c r="D305" t="str">
+        <v>speculaas pasta</v>
+      </c>
+      <c r="E305" t="str">
+        <v>speculoos spread</v>
+      </c>
+      <c r="F305" t="str">
+        <v/>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v/>
+      </c>
+      <c r="I305" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>vol-au-vent_koekje</v>
+      </c>
+      <c r="B306" t="str">
+        <v>vol-au-vent koekje</v>
+      </c>
+      <c r="C306" t="str">
+        <v>vol au vent koekje</v>
+      </c>
+      <c r="D306" t="str">
+        <v>vol-au-vent bladerdeeghapje</v>
+      </c>
+      <c r="E306" t="str">
+        <v/>
+      </c>
+      <c r="F306" t="str">
+        <v/>
+      </c>
+      <c r="G306" t="str">
+        <v/>
+      </c>
+      <c r="H306" t="str">
+        <v/>
+      </c>
+      <c r="I306" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>vol-au-vent_voorgemaakt</v>
+      </c>
+      <c r="B307" t="str">
+        <v>vol-au-vent voorgemaakt</v>
+      </c>
+      <c r="C307" t="str">
+        <v>vol au vent voorgemaakt</v>
+      </c>
+      <c r="D307" t="str">
+        <v>vol-au-vent gerecht</v>
+      </c>
+      <c r="E307" t="str">
+        <v/>
+      </c>
+      <c r="F307" t="str">
+        <v/>
+      </c>
+      <c r="G307" t="str">
+        <v/>
+      </c>
+      <c r="H307" t="str">
+        <v/>
+      </c>
+      <c r="I307" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>zuur_fruit_snoep</v>
+      </c>
+      <c r="B308" t="str">
+        <v>zuur fruit snoep</v>
+      </c>
+      <c r="C308" t="str">
+        <v>zure snoepjes</v>
+      </c>
+      <c r="D308" t="str">
+        <v>zuurtjes</v>
+      </c>
+      <c r="E308" t="str">
+        <v>zuur fruit</v>
+      </c>
+      <c r="F308" t="str">
+        <v/>
+      </c>
+      <c r="G308" t="str">
+        <v/>
+      </c>
+      <c r="H308" t="str">
+        <v/>
+      </c>
+      <c r="I308" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>vleesje_noë</v>
+      </c>
+      <c r="B309" t="str">
+        <v>vleesje noë</v>
+      </c>
+      <c r="C309" t="str">
+        <v/>
+      </c>
+      <c r="D309" t="str">
+        <v/>
+      </c>
+      <c r="E309" t="str">
+        <v/>
+      </c>
+      <c r="F309" t="str">
+        <v/>
+      </c>
+      <c r="G309" t="str">
+        <v/>
+      </c>
+      <c r="H309" t="str">
+        <v/>
+      </c>
+      <c r="I309" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I291"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I309"/>
   </ignoredErrors>
 </worksheet>
 </file>